--- a/Modelos IA/comparacion_predicciones2.xlsx
+++ b/Modelos IA/comparacion_predicciones2.xlsx
@@ -514,7 +514,7 @@
         <v>934</v>
       </c>
       <c r="C8" t="n">
-        <v>578.7173578445736</v>
+        <v>578.7173578445735</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         <v>628</v>
       </c>
       <c r="C10" t="n">
-        <v>535.0782776545594</v>
+        <v>535.0782776545593</v>
       </c>
     </row>
     <row r="11">
@@ -558,7 +558,7 @@
         <v>551</v>
       </c>
       <c r="C12" t="n">
-        <v>460.1203286123112</v>
+        <v>460.1203286123111</v>
       </c>
     </row>
     <row r="13">
@@ -679,7 +679,7 @@
         <v>1036</v>
       </c>
       <c r="C23" t="n">
-        <v>999.0961118639149</v>
+        <v>999.096111863915</v>
       </c>
     </row>
     <row r="24">
@@ -690,7 +690,7 @@
         <v>1103</v>
       </c>
       <c r="C24" t="n">
-        <v>929.4868595162076</v>
+        <v>929.4868595162078</v>
       </c>
     </row>
     <row r="25">
@@ -701,7 +701,7 @@
         <v>1048</v>
       </c>
       <c r="C25" t="n">
-        <v>1004.494838819108</v>
+        <v>1004.494838819107</v>
       </c>
     </row>
     <row r="26">
@@ -756,7 +756,7 @@
         <v>822</v>
       </c>
       <c r="C30" t="n">
-        <v>848.5816329975574</v>
+        <v>848.5816329975573</v>
       </c>
     </row>
     <row r="31">
@@ -822,7 +822,7 @@
         <v>300</v>
       </c>
       <c r="C36" t="n">
-        <v>350.4163269081673</v>
+        <v>350.4163269081672</v>
       </c>
     </row>
     <row r="37">
@@ -833,7 +833,7 @@
         <v>734</v>
       </c>
       <c r="C37" t="n">
-        <v>561.190820217439</v>
+        <v>561.1908202174388</v>
       </c>
     </row>
     <row r="38">
@@ -844,7 +844,7 @@
         <v>1068</v>
       </c>
       <c r="C38" t="n">
-        <v>802.5960689735044</v>
+        <v>802.5960689735043</v>
       </c>
     </row>
     <row r="39">
@@ -866,7 +866,7 @@
         <v>876</v>
       </c>
       <c r="C40" t="n">
-        <v>828.207247332651</v>
+        <v>828.2072473326509</v>
       </c>
     </row>
     <row r="41">
@@ -910,7 +910,7 @@
         <v>862</v>
       </c>
       <c r="C44" t="n">
-        <v>927.1029592421417</v>
+        <v>927.1029592421418</v>
       </c>
     </row>
     <row r="45">
@@ -921,7 +921,7 @@
         <v>868</v>
       </c>
       <c r="C45" t="n">
-        <v>881.4742366671584</v>
+        <v>881.4742366671582</v>
       </c>
     </row>
     <row r="46">
@@ -965,7 +965,7 @@
         <v>814</v>
       </c>
       <c r="C49" t="n">
-        <v>882.1235367578716</v>
+        <v>882.1235367578715</v>
       </c>
     </row>
     <row r="50">
@@ -976,7 +976,7 @@
         <v>773</v>
       </c>
       <c r="C50" t="n">
-        <v>889.9112036790127</v>
+        <v>889.9112036790128</v>
       </c>
     </row>
     <row r="51">
@@ -987,7 +987,7 @@
         <v>690</v>
       </c>
       <c r="C51" t="n">
-        <v>746.7508875745759</v>
+        <v>746.7508875745757</v>
       </c>
     </row>
     <row r="52">
@@ -1009,7 +1009,7 @@
         <v>420</v>
       </c>
       <c r="C53" t="n">
-        <v>452.7444399310939</v>
+        <v>452.7444399310938</v>
       </c>
     </row>
     <row r="54">
@@ -1108,7 +1108,7 @@
         <v>1022</v>
       </c>
       <c r="C62" t="n">
-        <v>788.5292176878139</v>
+        <v>788.5292176878141</v>
       </c>
     </row>
     <row r="63">
@@ -1119,7 +1119,7 @@
         <v>840</v>
       </c>
       <c r="C63" t="n">
-        <v>1160.749319127893</v>
+        <v>1160.749319127892</v>
       </c>
     </row>
     <row r="64">
@@ -1141,7 +1141,7 @@
         <v>952</v>
       </c>
       <c r="C65" t="n">
-        <v>979.3978902170734</v>
+        <v>979.3978902170736</v>
       </c>
     </row>
     <row r="66">
@@ -1152,7 +1152,7 @@
         <v>937</v>
       </c>
       <c r="C66" t="n">
-        <v>982.3485706582367</v>
+        <v>982.3485706582366</v>
       </c>
     </row>
     <row r="67">
@@ -1185,7 +1185,7 @@
         <v>866</v>
       </c>
       <c r="C69" t="n">
-        <v>857.5021260272373</v>
+        <v>857.5021260272371</v>
       </c>
     </row>
     <row r="70">
@@ -1240,7 +1240,7 @@
         <v>796</v>
       </c>
       <c r="C74" t="n">
-        <v>931.5635513978918</v>
+        <v>931.563551397892</v>
       </c>
     </row>
     <row r="75">
@@ -1251,7 +1251,7 @@
         <v>726</v>
       </c>
       <c r="C75" t="n">
-        <v>757.5498550446417</v>
+        <v>757.5498550446416</v>
       </c>
     </row>
     <row r="76">
@@ -1273,7 +1273,7 @@
         <v>456</v>
       </c>
       <c r="C77" t="n">
-        <v>472.881134631058</v>
+        <v>472.8811346310579</v>
       </c>
     </row>
     <row r="78">
@@ -1350,7 +1350,7 @@
         <v>310</v>
       </c>
       <c r="C84" t="n">
-        <v>215.7464421389564</v>
+        <v>215.7464421389565</v>
       </c>
     </row>
     <row r="85">
@@ -1482,7 +1482,7 @@
         <v>800</v>
       </c>
       <c r="C96" t="n">
-        <v>756.8210279434982</v>
+        <v>756.8210279434984</v>
       </c>
     </row>
     <row r="97">
@@ -1493,7 +1493,7 @@
         <v>812</v>
       </c>
       <c r="C97" t="n">
-        <v>787.4243596737062</v>
+        <v>787.4243596737064</v>
       </c>
     </row>
     <row r="98">
@@ -1526,7 +1526,7 @@
         <v>670</v>
       </c>
       <c r="C100" t="n">
-        <v>760.1889637344497</v>
+        <v>760.1889637344495</v>
       </c>
     </row>
     <row r="101">
@@ -1559,7 +1559,7 @@
         <v>953</v>
       </c>
       <c r="C103" t="n">
-        <v>881.166122999653</v>
+        <v>881.1661229996531</v>
       </c>
     </row>
     <row r="104">
@@ -1647,7 +1647,7 @@
         <v>630</v>
       </c>
       <c r="C111" t="n">
-        <v>532.2294158343393</v>
+        <v>532.2294158343394</v>
       </c>
     </row>
     <row r="112">
@@ -1746,7 +1746,7 @@
         <v>1122</v>
       </c>
       <c r="C120" t="n">
-        <v>997.1834290551037</v>
+        <v>997.1834290551039</v>
       </c>
     </row>
     <row r="121">
@@ -1867,7 +1867,7 @@
         <v>159</v>
       </c>
       <c r="C131" t="n">
-        <v>182.4102401772391</v>
+        <v>182.410240177239</v>
       </c>
     </row>
     <row r="132">
@@ -1878,7 +1878,7 @@
         <v>310</v>
       </c>
       <c r="C132" t="n">
-        <v>349.2478216925179</v>
+        <v>349.2478216925178</v>
       </c>
     </row>
     <row r="133">
@@ -1900,7 +1900,7 @@
         <v>1058</v>
       </c>
       <c r="C134" t="n">
-        <v>797.6089862010095</v>
+        <v>797.6089862010094</v>
       </c>
     </row>
     <row r="135">
@@ -1911,7 +1911,7 @@
         <v>858</v>
       </c>
       <c r="C135" t="n">
-        <v>919.1320321145785</v>
+        <v>919.1320321145786</v>
       </c>
     </row>
     <row r="136">
@@ -1955,7 +1955,7 @@
         <v>938</v>
       </c>
       <c r="C139" t="n">
-        <v>1018.191986922155</v>
+        <v>1018.191986922156</v>
       </c>
     </row>
     <row r="140">
@@ -2010,7 +2010,7 @@
         <v>894</v>
       </c>
       <c r="C144" t="n">
-        <v>761.4710958003237</v>
+        <v>761.4710958003238</v>
       </c>
     </row>
     <row r="145">
@@ -2021,7 +2021,7 @@
         <v>902</v>
       </c>
       <c r="C145" t="n">
-        <v>960.9206669352513</v>
+        <v>960.9206669352517</v>
       </c>
     </row>
     <row r="146">
@@ -2032,7 +2032,7 @@
         <v>820</v>
       </c>
       <c r="C146" t="n">
-        <v>904.0188652647765</v>
+        <v>904.0188652647764</v>
       </c>
     </row>
     <row r="147">
@@ -2054,7 +2054,7 @@
         <v>571</v>
       </c>
       <c r="C148" t="n">
-        <v>649.2911021430223</v>
+        <v>649.2911021430224</v>
       </c>
     </row>
     <row r="149">
@@ -2164,7 +2164,7 @@
         <v>1168</v>
       </c>
       <c r="C158" t="n">
-        <v>808.8862229557105</v>
+        <v>808.8862229557107</v>
       </c>
     </row>
     <row r="159">
@@ -2241,7 +2241,7 @@
         <v>938</v>
       </c>
       <c r="C165" t="n">
-        <v>925.7612722055139</v>
+        <v>925.7612722055138</v>
       </c>
     </row>
     <row r="166">
@@ -2252,7 +2252,7 @@
         <v>851</v>
       </c>
       <c r="C166" t="n">
-        <v>774.571410471082</v>
+        <v>774.5714104710819</v>
       </c>
     </row>
     <row r="167">
@@ -2263,7 +2263,7 @@
         <v>884</v>
       </c>
       <c r="C167" t="n">
-        <v>823.2745253131245</v>
+        <v>823.2745253131243</v>
       </c>
     </row>
     <row r="168">
@@ -2285,7 +2285,7 @@
         <v>966</v>
       </c>
       <c r="C169" t="n">
-        <v>958.0526481738542</v>
+        <v>958.0526481738545</v>
       </c>
     </row>
     <row r="170">
@@ -2296,7 +2296,7 @@
         <v>872</v>
       </c>
       <c r="C170" t="n">
-        <v>964.3373672998684</v>
+        <v>964.3373672998688</v>
       </c>
     </row>
     <row r="171">
@@ -2307,7 +2307,7 @@
         <v>770</v>
       </c>
       <c r="C171" t="n">
-        <v>788.4527619331642</v>
+        <v>788.4527619331643</v>
       </c>
     </row>
     <row r="172">
@@ -2318,7 +2318,7 @@
         <v>608</v>
       </c>
       <c r="C172" t="n">
-        <v>677.6300806055322</v>
+        <v>677.6300806055319</v>
       </c>
     </row>
     <row r="173">
@@ -2428,7 +2428,7 @@
         <v>886</v>
       </c>
       <c r="C182" t="n">
-        <v>844.9540030407319</v>
+        <v>844.954003040732</v>
       </c>
     </row>
     <row r="183">
@@ -2450,7 +2450,7 @@
         <v>906</v>
       </c>
       <c r="C184" t="n">
-        <v>915.2070103515615</v>
+        <v>915.2070103515613</v>
       </c>
     </row>
     <row r="185">
@@ -2461,7 +2461,7 @@
         <v>959</v>
       </c>
       <c r="C185" t="n">
-        <v>984.2579670336864</v>
+        <v>984.2579670336863</v>
       </c>
     </row>
     <row r="186">
@@ -2505,7 +2505,7 @@
         <v>936</v>
       </c>
       <c r="C189" t="n">
-        <v>891.6619061606867</v>
+        <v>891.6619061606866</v>
       </c>
     </row>
     <row r="190">
@@ -2538,7 +2538,7 @@
         <v>958</v>
       </c>
       <c r="C192" t="n">
-        <v>872.7661091779654</v>
+        <v>872.7661091779653</v>
       </c>
     </row>
     <row r="193">
@@ -2549,7 +2549,7 @@
         <v>997</v>
       </c>
       <c r="C193" t="n">
-        <v>897.9665394610699</v>
+        <v>897.9665394610697</v>
       </c>
     </row>
     <row r="194">
@@ -2560,7 +2560,7 @@
         <v>906</v>
       </c>
       <c r="C194" t="n">
-        <v>1013.972086826991</v>
+        <v>1013.972086826992</v>
       </c>
     </row>
     <row r="195">
@@ -2582,7 +2582,7 @@
         <v>615</v>
       </c>
       <c r="C196" t="n">
-        <v>725.3601124111196</v>
+        <v>725.3601124111195</v>
       </c>
     </row>
     <row r="197">
@@ -2681,7 +2681,7 @@
         <v>788</v>
       </c>
       <c r="C205" t="n">
-        <v>545.6688080929891</v>
+        <v>545.668808092989</v>
       </c>
     </row>
     <row r="206">
@@ -2725,7 +2725,7 @@
         <v>996</v>
       </c>
       <c r="C209" t="n">
-        <v>980.3137366446931</v>
+        <v>980.3137366446932</v>
       </c>
     </row>
     <row r="210">
@@ -2758,7 +2758,7 @@
         <v>1027</v>
       </c>
       <c r="C212" t="n">
-        <v>929.7100833813489</v>
+        <v>929.7100833813488</v>
       </c>
     </row>
     <row r="213">
@@ -2813,7 +2813,7 @@
         <v>943</v>
       </c>
       <c r="C217" t="n">
-        <v>954.6731577298177</v>
+        <v>954.6731577298179</v>
       </c>
     </row>
     <row r="218">
@@ -2824,7 +2824,7 @@
         <v>922</v>
       </c>
       <c r="C218" t="n">
-        <v>965.9480759855271</v>
+        <v>965.9480759855272</v>
       </c>
     </row>
     <row r="219">
@@ -2835,7 +2835,7 @@
         <v>874</v>
       </c>
       <c r="C219" t="n">
-        <v>889.1420799993861</v>
+        <v>889.1420799993859</v>
       </c>
     </row>
     <row r="220">
@@ -2846,7 +2846,7 @@
         <v>737</v>
       </c>
       <c r="C220" t="n">
-        <v>783.2134743215965</v>
+        <v>783.2134743215968</v>
       </c>
     </row>
     <row r="221">
@@ -2857,7 +2857,7 @@
         <v>608</v>
       </c>
       <c r="C221" t="n">
-        <v>614.3883415929489</v>
+        <v>614.3883415929488</v>
       </c>
     </row>
     <row r="222">
@@ -2934,7 +2934,7 @@
         <v>585</v>
       </c>
       <c r="C228" t="n">
-        <v>428.674052352289</v>
+        <v>428.6740523522891</v>
       </c>
     </row>
     <row r="229">
@@ -2945,7 +2945,7 @@
         <v>636</v>
       </c>
       <c r="C229" t="n">
-        <v>543.941543267905</v>
+        <v>543.9415432679049</v>
       </c>
     </row>
     <row r="230">
@@ -2978,7 +2978,7 @@
         <v>948</v>
       </c>
       <c r="C232" t="n">
-        <v>720.8789225081391</v>
+        <v>720.8789225081392</v>
       </c>
     </row>
     <row r="233">
@@ -2989,7 +2989,7 @@
         <v>1210</v>
       </c>
       <c r="C233" t="n">
-        <v>905.223569551892</v>
+        <v>905.2235695518922</v>
       </c>
     </row>
     <row r="234">
@@ -3132,7 +3132,7 @@
         <v>977</v>
       </c>
       <c r="C246" t="n">
-        <v>975.7135867747627</v>
+        <v>975.7135867747625</v>
       </c>
     </row>
     <row r="247">
@@ -3187,7 +3187,7 @@
         <v>186</v>
       </c>
       <c r="C251" t="n">
-        <v>169.114454168992</v>
+        <v>169.1144541689921</v>
       </c>
     </row>
     <row r="252">
@@ -3198,7 +3198,7 @@
         <v>324</v>
       </c>
       <c r="C252" t="n">
-        <v>321.251378209442</v>
+        <v>321.2513782094421</v>
       </c>
     </row>
     <row r="253">
@@ -3209,7 +3209,7 @@
         <v>772</v>
       </c>
       <c r="C253" t="n">
-        <v>557.8584809432867</v>
+        <v>557.8584809432868</v>
       </c>
     </row>
     <row r="254">
@@ -3275,7 +3275,7 @@
         <v>966</v>
       </c>
       <c r="C259" t="n">
-        <v>999.6279577972964</v>
+        <v>999.6279577972963</v>
       </c>
     </row>
     <row r="260">
@@ -3286,7 +3286,7 @@
         <v>958</v>
       </c>
       <c r="C260" t="n">
-        <v>966.7579894313604</v>
+        <v>966.7579894313608</v>
       </c>
     </row>
     <row r="261">
@@ -3308,7 +3308,7 @@
         <v>883</v>
       </c>
       <c r="C262" t="n">
-        <v>825.6990957061305</v>
+        <v>825.6990957061303</v>
       </c>
     </row>
     <row r="263">
@@ -3319,7 +3319,7 @@
         <v>884</v>
       </c>
       <c r="C263" t="n">
-        <v>807.8635245113877</v>
+        <v>807.8635245113875</v>
       </c>
     </row>
     <row r="264">
@@ -3341,7 +3341,7 @@
         <v>932</v>
       </c>
       <c r="C265" t="n">
-        <v>959.8825832719125</v>
+        <v>959.8825832719127</v>
       </c>
     </row>
     <row r="266">
@@ -3352,7 +3352,7 @@
         <v>844</v>
       </c>
       <c r="C266" t="n">
-        <v>946.2173200525115</v>
+        <v>946.2173200525114</v>
       </c>
     </row>
     <row r="267">
@@ -3473,7 +3473,7 @@
         <v>788</v>
       </c>
       <c r="C277" t="n">
-        <v>555.1740515191403</v>
+        <v>555.1740515191404</v>
       </c>
     </row>
     <row r="278">
@@ -3484,7 +3484,7 @@
         <v>890</v>
       </c>
       <c r="C278" t="n">
-        <v>887.3148480133351</v>
+        <v>887.3148480133353</v>
       </c>
     </row>
     <row r="279">
@@ -3506,7 +3506,7 @@
         <v>943</v>
       </c>
       <c r="C280" t="n">
-        <v>957.851048833912</v>
+        <v>957.8510488339122</v>
       </c>
     </row>
     <row r="281">
@@ -3605,7 +3605,7 @@
         <v>907</v>
       </c>
       <c r="C289" t="n">
-        <v>950.3571305528391</v>
+        <v>950.357130552839</v>
       </c>
     </row>
     <row r="290">
@@ -3770,7 +3770,7 @@
         <v>881</v>
       </c>
       <c r="C304" t="n">
-        <v>966.5764289803586</v>
+        <v>966.5764289803587</v>
       </c>
     </row>
     <row r="305">
@@ -3781,7 +3781,7 @@
         <v>942</v>
       </c>
       <c r="C305" t="n">
-        <v>989.494451975717</v>
+        <v>989.4944519757169</v>
       </c>
     </row>
     <row r="306">
@@ -3792,7 +3792,7 @@
         <v>936</v>
       </c>
       <c r="C306" t="n">
-        <v>984.53827702022</v>
+        <v>984.5382770202199</v>
       </c>
     </row>
     <row r="307">
@@ -3803,7 +3803,7 @@
         <v>970</v>
       </c>
       <c r="C307" t="n">
-        <v>960.3828625276037</v>
+        <v>960.3828625276038</v>
       </c>
     </row>
     <row r="308">
@@ -3814,7 +3814,7 @@
         <v>950</v>
       </c>
       <c r="C308" t="n">
-        <v>969.828526658927</v>
+        <v>969.8285266589273</v>
       </c>
     </row>
     <row r="309">
@@ -3836,7 +3836,7 @@
         <v>856</v>
       </c>
       <c r="C310" t="n">
-        <v>847.3067196177212</v>
+        <v>847.3067196177213</v>
       </c>
     </row>
     <row r="311">
@@ -3880,7 +3880,7 @@
         <v>886</v>
       </c>
       <c r="C314" t="n">
-        <v>943.6970873060266</v>
+        <v>943.6970873060263</v>
       </c>
     </row>
     <row r="315">
@@ -3913,7 +3913,7 @@
         <v>500</v>
       </c>
       <c r="C317" t="n">
-        <v>594.2551257297613</v>
+        <v>594.2551257297614</v>
       </c>
     </row>
     <row r="318">
@@ -3935,7 +3935,7 @@
         <v>302</v>
       </c>
       <c r="C319" t="n">
-        <v>279.3981097669033</v>
+        <v>279.3981097669032</v>
       </c>
     </row>
     <row r="320">
@@ -3979,7 +3979,7 @@
         <v>164</v>
       </c>
       <c r="C323" t="n">
-        <v>176.2795014682241</v>
+        <v>176.2795014682242</v>
       </c>
     </row>
     <row r="324">
@@ -4012,7 +4012,7 @@
         <v>825</v>
       </c>
       <c r="C326" t="n">
-        <v>891.1320532451223</v>
+        <v>891.1320532451224</v>
       </c>
     </row>
     <row r="327">
@@ -4045,7 +4045,7 @@
         <v>936</v>
       </c>
       <c r="C329" t="n">
-        <v>992.3010303672735</v>
+        <v>992.3010303672734</v>
       </c>
     </row>
     <row r="330">
@@ -4089,7 +4089,7 @@
         <v>902</v>
       </c>
       <c r="C333" t="n">
-        <v>986.412982739633</v>
+        <v>986.4129827396329</v>
       </c>
     </row>
     <row r="334">
@@ -4122,7 +4122,7 @@
         <v>876</v>
       </c>
       <c r="C336" t="n">
-        <v>904.0120188053143</v>
+        <v>904.0120188053141</v>
       </c>
     </row>
     <row r="337">
@@ -4210,7 +4210,7 @@
         <v>1059</v>
       </c>
       <c r="C344" t="n">
-        <v>891.3180790928318</v>
+        <v>891.3180790928319</v>
       </c>
     </row>
     <row r="345">
@@ -4221,7 +4221,7 @@
         <v>860</v>
       </c>
       <c r="C345" t="n">
-        <v>732.1413732209735</v>
+        <v>732.1413732209734</v>
       </c>
     </row>
     <row r="346">
@@ -4232,7 +4232,7 @@
         <v>789</v>
       </c>
       <c r="C346" t="n">
-        <v>662.8324694323675</v>
+        <v>662.8324694323677</v>
       </c>
     </row>
     <row r="347">
@@ -4342,7 +4342,7 @@
         <v>1662</v>
       </c>
       <c r="C356" t="n">
-        <v>1587.62358274287</v>
+        <v>1587.623582742869</v>
       </c>
     </row>
     <row r="357">
@@ -4353,7 +4353,7 @@
         <v>1469</v>
       </c>
       <c r="C357" t="n">
-        <v>1567.447158147824</v>
+        <v>1567.447158147825</v>
       </c>
     </row>
     <row r="358">
@@ -4452,7 +4452,7 @@
         <v>988</v>
       </c>
       <c r="C366" t="n">
-        <v>945.1546625050582</v>
+        <v>945.1546625050584</v>
       </c>
     </row>
     <row r="367">
@@ -4507,7 +4507,7 @@
         <v>185</v>
       </c>
       <c r="C371" t="n">
-        <v>174.2043897797019</v>
+        <v>174.2043897797018</v>
       </c>
     </row>
     <row r="372">
@@ -4518,7 +4518,7 @@
         <v>400</v>
       </c>
       <c r="C372" t="n">
-        <v>379.0136886904939</v>
+        <v>379.0136886904938</v>
       </c>
     </row>
     <row r="373">
@@ -4705,7 +4705,7 @@
         <v>532</v>
       </c>
       <c r="C389" t="n">
-        <v>540.649985825048</v>
+        <v>540.6499858250481</v>
       </c>
     </row>
     <row r="390">
@@ -4760,7 +4760,7 @@
         <v>124</v>
       </c>
       <c r="C394" t="n">
-        <v>120.9481490477972</v>
+        <v>120.9481490477973</v>
       </c>
     </row>
     <row r="395">
@@ -4793,7 +4793,7 @@
         <v>856</v>
       </c>
       <c r="C397" t="n">
-        <v>808.7902563896107</v>
+        <v>808.7902563896106</v>
       </c>
     </row>
     <row r="398">
@@ -4958,7 +4958,7 @@
         <v>718</v>
       </c>
       <c r="C412" t="n">
-        <v>839.4390803339238</v>
+        <v>839.4390803339239</v>
       </c>
     </row>
     <row r="413">
@@ -4991,7 +4991,7 @@
         <v>386</v>
       </c>
       <c r="C415" t="n">
-        <v>371.7741201775944</v>
+        <v>371.7741201775943</v>
       </c>
     </row>
     <row r="416">
@@ -5057,7 +5057,7 @@
         <v>881</v>
       </c>
       <c r="C421" t="n">
-        <v>807.0339914410042</v>
+        <v>807.033991441004</v>
       </c>
     </row>
     <row r="422">
@@ -5134,7 +5134,7 @@
         <v>1125</v>
       </c>
       <c r="C428" t="n">
-        <v>1133.353039782116</v>
+        <v>1133.353039782115</v>
       </c>
     </row>
     <row r="429">
@@ -5167,7 +5167,7 @@
         <v>1109</v>
       </c>
       <c r="C431" t="n">
-        <v>1068.933880225704</v>
+        <v>1068.933880225703</v>
       </c>
     </row>
     <row r="432">
@@ -5211,7 +5211,7 @@
         <v>988</v>
       </c>
       <c r="C435" t="n">
-        <v>1048.710432196062</v>
+        <v>1048.710432196063</v>
       </c>
     </row>
     <row r="436">
@@ -5233,7 +5233,7 @@
         <v>656</v>
       </c>
       <c r="C437" t="n">
-        <v>701.0280094412909</v>
+        <v>701.028009441291</v>
       </c>
     </row>
     <row r="438">
@@ -5420,7 +5420,7 @@
         <v>1033</v>
       </c>
       <c r="C454" t="n">
-        <v>1014.468304380585</v>
+        <v>1014.468304380586</v>
       </c>
     </row>
     <row r="455">
@@ -5563,7 +5563,7 @@
         <v>936</v>
       </c>
       <c r="C467" t="n">
-        <v>751.183362926305</v>
+        <v>751.1833629263049</v>
       </c>
     </row>
     <row r="468">
@@ -5574,7 +5574,7 @@
         <v>916</v>
       </c>
       <c r="C468" t="n">
-        <v>654.289013631559</v>
+        <v>654.2890136315589</v>
       </c>
     </row>
     <row r="469">
@@ -5585,7 +5585,7 @@
         <v>672</v>
       </c>
       <c r="C469" t="n">
-        <v>650.4001353983875</v>
+        <v>650.4001353983874</v>
       </c>
     </row>
     <row r="470">
@@ -5596,7 +5596,7 @@
         <v>586</v>
       </c>
       <c r="C470" t="n">
-        <v>684.7335746827823</v>
+        <v>684.7335746827825</v>
       </c>
     </row>
     <row r="471">
@@ -5684,7 +5684,7 @@
         <v>246</v>
       </c>
       <c r="C478" t="n">
-        <v>467.2082656537604</v>
+        <v>467.2082656537605</v>
       </c>
     </row>
     <row r="479">
@@ -5750,7 +5750,7 @@
         <v>492</v>
       </c>
       <c r="C484" t="n">
-        <v>469.619959774234</v>
+        <v>469.6199597742341</v>
       </c>
     </row>
     <row r="485">
@@ -5761,7 +5761,7 @@
         <v>912</v>
       </c>
       <c r="C485" t="n">
-        <v>468.1405651565528</v>
+        <v>468.1405651565527</v>
       </c>
     </row>
     <row r="486">
@@ -5805,7 +5805,7 @@
         <v>134</v>
       </c>
       <c r="C489" t="n">
-        <v>140.8121980134693</v>
+        <v>140.8121980134694</v>
       </c>
     </row>
     <row r="490">
@@ -5926,7 +5926,7 @@
         <v>1128</v>
       </c>
       <c r="C500" t="n">
-        <v>1163.727097324854</v>
+        <v>1163.727097324855</v>
       </c>
     </row>
     <row r="501">
@@ -6036,7 +6036,7 @@
         <v>406</v>
       </c>
       <c r="C510" t="n">
-        <v>430.6542586537091</v>
+        <v>430.654258653709</v>
       </c>
     </row>
     <row r="511">
@@ -6069,7 +6069,7 @@
         <v>136</v>
       </c>
       <c r="C513" t="n">
-        <v>143.4267036316916</v>
+        <v>143.4267036316915</v>
       </c>
     </row>
     <row r="514">
@@ -6157,7 +6157,7 @@
         <v>1182</v>
       </c>
       <c r="C521" t="n">
-        <v>1157.302317301743</v>
+        <v>1157.302317301742</v>
       </c>
     </row>
     <row r="522">
@@ -6300,7 +6300,7 @@
         <v>474</v>
       </c>
       <c r="C534" t="n">
-        <v>469.9500365794725</v>
+        <v>469.9500365794726</v>
       </c>
     </row>
     <row r="535">
@@ -6465,7 +6465,7 @@
         <v>1097</v>
       </c>
       <c r="C549" t="n">
-        <v>1147.0275045868</v>
+        <v>1147.027504586801</v>
       </c>
     </row>
     <row r="550">
@@ -6542,7 +6542,7 @@
         <v>813</v>
       </c>
       <c r="C556" t="n">
-        <v>886.8984234723554</v>
+        <v>886.8984234723553</v>
       </c>
     </row>
     <row r="557">
@@ -6553,7 +6553,7 @@
         <v>678</v>
       </c>
       <c r="C557" t="n">
-        <v>703.9891172380317</v>
+        <v>703.9891172380318</v>
       </c>
     </row>
     <row r="558">
@@ -6718,7 +6718,7 @@
         <v>1134</v>
       </c>
       <c r="C572" t="n">
-        <v>1145.659682207094</v>
+        <v>1145.659682207095</v>
       </c>
     </row>
     <row r="573">
@@ -6806,7 +6806,7 @@
         <v>850</v>
       </c>
       <c r="C580" t="n">
-        <v>939.9111716016082</v>
+        <v>939.9111716016081</v>
       </c>
     </row>
     <row r="581">
@@ -6817,7 +6817,7 @@
         <v>701</v>
       </c>
       <c r="C581" t="n">
-        <v>725.2205276059858</v>
+        <v>725.2205276059857</v>
       </c>
     </row>
     <row r="582">
@@ -6828,7 +6828,7 @@
         <v>667</v>
       </c>
       <c r="C582" t="n">
-        <v>717.5618473384569</v>
+        <v>717.5618473384567</v>
       </c>
     </row>
     <row r="583">
@@ -6872,7 +6872,7 @@
         <v>962</v>
       </c>
       <c r="C586" t="n">
-        <v>956.9243252655293</v>
+        <v>956.9243252655292</v>
       </c>
     </row>
     <row r="587">
@@ -6883,7 +6883,7 @@
         <v>932</v>
       </c>
       <c r="C587" t="n">
-        <v>722.4929972134295</v>
+        <v>722.4929972134296</v>
       </c>
     </row>
     <row r="588">
@@ -6905,7 +6905,7 @@
         <v>817</v>
       </c>
       <c r="C589" t="n">
-        <v>705.6173323300777</v>
+        <v>705.6173323300779</v>
       </c>
     </row>
     <row r="590">
@@ -7004,7 +7004,7 @@
         <v>1634</v>
       </c>
       <c r="C598" t="n">
-        <v>1427.827455132788</v>
+        <v>1427.827455132787</v>
       </c>
     </row>
     <row r="599">
@@ -7169,7 +7169,7 @@
         <v>859</v>
       </c>
       <c r="C613" t="n">
-        <v>808.9250655141955</v>
+        <v>808.9250655141956</v>
       </c>
     </row>
     <row r="614">
@@ -7378,7 +7378,7 @@
         <v>183</v>
       </c>
       <c r="C632" t="n">
-        <v>178.9242299841162</v>
+        <v>178.9242299841163</v>
       </c>
     </row>
     <row r="633">
@@ -7411,7 +7411,7 @@
         <v>173</v>
       </c>
       <c r="C635" t="n">
-        <v>182.0958205520972</v>
+        <v>182.0958205520973</v>
       </c>
     </row>
     <row r="636">
@@ -7488,7 +7488,7 @@
         <v>1215</v>
       </c>
       <c r="C642" t="n">
-        <v>1169.354249617191</v>
+        <v>1169.354249617192</v>
       </c>
     </row>
     <row r="643">
@@ -7598,7 +7598,7 @@
         <v>716</v>
       </c>
       <c r="C652" t="n">
-        <v>863.3791098737347</v>
+        <v>863.3791098737346</v>
       </c>
     </row>
     <row r="653">
@@ -7653,7 +7653,7 @@
         <v>213</v>
       </c>
       <c r="C657" t="n">
-        <v>235.853124331801</v>
+        <v>235.8531243318011</v>
       </c>
     </row>
     <row r="658">
@@ -7664,7 +7664,7 @@
         <v>186</v>
       </c>
       <c r="C658" t="n">
-        <v>198.0935642492147</v>
+        <v>198.0935642492148</v>
       </c>
     </row>
     <row r="659">
@@ -7785,7 +7785,7 @@
         <v>1086</v>
       </c>
       <c r="C669" t="n">
-        <v>1160.413352070119</v>
+        <v>1160.41335207012</v>
       </c>
     </row>
     <row r="670">
@@ -7873,7 +7873,7 @@
         <v>749</v>
       </c>
       <c r="C677" t="n">
-        <v>692.1809275811449</v>
+        <v>692.1809275811448</v>
       </c>
     </row>
     <row r="678">
@@ -7884,7 +7884,7 @@
         <v>612</v>
       </c>
       <c r="C678" t="n">
-        <v>598.2258513171176</v>
+        <v>598.2258513171175</v>
       </c>
     </row>
     <row r="679">
@@ -7895,7 +7895,7 @@
         <v>458</v>
       </c>
       <c r="C679" t="n">
-        <v>428.1882127302087</v>
+        <v>428.1882127302088</v>
       </c>
     </row>
     <row r="680">
@@ -7939,7 +7939,7 @@
         <v>250</v>
       </c>
       <c r="C683" t="n">
-        <v>233.3131824354314</v>
+        <v>233.3131824354315</v>
       </c>
     </row>
     <row r="684">
@@ -7950,7 +7950,7 @@
         <v>426</v>
       </c>
       <c r="C684" t="n">
-        <v>378.6825172618268</v>
+        <v>378.6825172618267</v>
       </c>
     </row>
     <row r="685">
@@ -7961,7 +7961,7 @@
         <v>1071</v>
       </c>
       <c r="C685" t="n">
-        <v>775.8468373095093</v>
+        <v>775.8468373095094</v>
       </c>
     </row>
     <row r="686">
@@ -8170,7 +8170,7 @@
         <v>1363</v>
       </c>
       <c r="C704" t="n">
-        <v>1352.600589016001</v>
+        <v>1352.600589016</v>
       </c>
     </row>
     <row r="705">
@@ -8225,7 +8225,7 @@
         <v>756</v>
       </c>
       <c r="C709" t="n">
-        <v>746.2571601262637</v>
+        <v>746.2571601262638</v>
       </c>
     </row>
     <row r="710">
@@ -8258,7 +8258,7 @@
         <v>394</v>
       </c>
       <c r="C712" t="n">
-        <v>794.805542329335</v>
+        <v>794.8055423293349</v>
       </c>
     </row>
     <row r="713">
@@ -8269,7 +8269,7 @@
         <v>760</v>
       </c>
       <c r="C713" t="n">
-        <v>786.6952437122113</v>
+        <v>786.6952437122112</v>
       </c>
     </row>
     <row r="714">
@@ -8379,7 +8379,7 @@
         <v>1566</v>
       </c>
       <c r="C723" t="n">
-        <v>1550.225310103897</v>
+        <v>1550.225310103898</v>
       </c>
     </row>
     <row r="724">
@@ -8434,7 +8434,7 @@
         <v>177</v>
       </c>
       <c r="C728" t="n">
-        <v>184.2013766778924</v>
+        <v>184.2013766778925</v>
       </c>
     </row>
     <row r="729">
@@ -8555,7 +8555,7 @@
         <v>1180</v>
       </c>
       <c r="C739" t="n">
-        <v>1180.394587501063</v>
+        <v>1180.394587501062</v>
       </c>
     </row>
     <row r="740">
@@ -8599,7 +8599,7 @@
         <v>1132</v>
       </c>
       <c r="C743" t="n">
-        <v>1076.931299374158</v>
+        <v>1076.931299374157</v>
       </c>
     </row>
     <row r="744">
@@ -8632,7 +8632,7 @@
         <v>1046</v>
       </c>
       <c r="C746" t="n">
-        <v>1125.337825565513</v>
+        <v>1125.337825565514</v>
       </c>
     </row>
     <row r="747">
@@ -8643,7 +8643,7 @@
         <v>855</v>
       </c>
       <c r="C747" t="n">
-        <v>947.783013218996</v>
+        <v>947.7830132189961</v>
       </c>
     </row>
     <row r="748">
@@ -8676,7 +8676,7 @@
         <v>398</v>
       </c>
       <c r="C750" t="n">
-        <v>367.5907996241811</v>
+        <v>367.5907996241812</v>
       </c>
     </row>
     <row r="751">
@@ -8797,7 +8797,7 @@
         <v>1396</v>
       </c>
       <c r="C761" t="n">
-        <v>1195.07106652073</v>
+        <v>1195.071066520729</v>
       </c>
     </row>
     <row r="762">
@@ -8940,7 +8940,7 @@
         <v>479</v>
       </c>
       <c r="C774" t="n">
-        <v>467.6829095484556</v>
+        <v>467.6829095484557</v>
       </c>
     </row>
     <row r="775">
@@ -9182,7 +9182,7 @@
         <v>786</v>
       </c>
       <c r="C796" t="n">
-        <v>860.5131321735311</v>
+        <v>860.5131321735312</v>
       </c>
     </row>
     <row r="797">
@@ -9193,7 +9193,7 @@
         <v>684</v>
       </c>
       <c r="C797" t="n">
-        <v>700.185815940043</v>
+        <v>700.1858159400431</v>
       </c>
     </row>
     <row r="798">
@@ -9215,7 +9215,7 @@
         <v>459</v>
       </c>
       <c r="C799" t="n">
-        <v>429.5526168799994</v>
+        <v>429.5526168799993</v>
       </c>
     </row>
     <row r="800">
@@ -9446,7 +9446,7 @@
         <v>850</v>
       </c>
       <c r="C820" t="n">
-        <v>870.4234273018583</v>
+        <v>870.4234273018585</v>
       </c>
     </row>
     <row r="821">
@@ -9457,7 +9457,7 @@
         <v>728</v>
       </c>
       <c r="C821" t="n">
-        <v>738.8329263842106</v>
+        <v>738.8329263842104</v>
       </c>
     </row>
     <row r="822">
@@ -9468,7 +9468,7 @@
         <v>662</v>
       </c>
       <c r="C822" t="n">
-        <v>652.2510712616836</v>
+        <v>652.2510712616837</v>
       </c>
     </row>
     <row r="823">
@@ -9545,7 +9545,7 @@
         <v>872</v>
       </c>
       <c r="C829" t="n">
-        <v>685.8347351532191</v>
+        <v>685.834735153219</v>
       </c>
     </row>
     <row r="830">
@@ -9578,7 +9578,7 @@
         <v>1114</v>
       </c>
       <c r="C832" t="n">
-        <v>848.4880806840254</v>
+        <v>848.4880806840251</v>
       </c>
     </row>
     <row r="833">
@@ -9633,7 +9633,7 @@
         <v>1762</v>
       </c>
       <c r="C837" t="n">
-        <v>1689.695353821211</v>
+        <v>1689.695353821212</v>
       </c>
     </row>
     <row r="838">
@@ -9655,7 +9655,7 @@
         <v>1750</v>
       </c>
       <c r="C839" t="n">
-        <v>1480.32247618666</v>
+        <v>1480.322476186659</v>
       </c>
     </row>
     <row r="840">
@@ -9798,7 +9798,7 @@
         <v>409</v>
       </c>
       <c r="C852" t="n">
-        <v>373.067296956052</v>
+        <v>373.0672969560521</v>
       </c>
     </row>
     <row r="853">
@@ -9941,7 +9941,7 @@
         <v>1156</v>
       </c>
       <c r="C865" t="n">
-        <v>1118.499963181425</v>
+        <v>1118.499963181424</v>
       </c>
     </row>
     <row r="866">
@@ -9974,7 +9974,7 @@
         <v>666</v>
       </c>
       <c r="C868" t="n">
-        <v>715.648251911933</v>
+        <v>715.6482519119331</v>
       </c>
     </row>
     <row r="869">
@@ -10084,7 +10084,7 @@
         <v>1498</v>
       </c>
       <c r="C878" t="n">
-        <v>1336.233685700559</v>
+        <v>1336.233685700558</v>
       </c>
     </row>
     <row r="879">
@@ -10117,7 +10117,7 @@
         <v>1211</v>
       </c>
       <c r="C881" t="n">
-        <v>1184.23386452537</v>
+        <v>1184.233864525371</v>
       </c>
     </row>
     <row r="882">
@@ -10172,7 +10172,7 @@
         <v>1158</v>
       </c>
       <c r="C886" t="n">
-        <v>1188.085492902943</v>
+        <v>1188.085492902944</v>
       </c>
     </row>
     <row r="887">
@@ -10249,7 +10249,7 @@
         <v>788</v>
       </c>
       <c r="C893" t="n">
-        <v>798.2905406530361</v>
+        <v>798.2905406530363</v>
       </c>
     </row>
     <row r="894">
@@ -10260,7 +10260,7 @@
         <v>806</v>
       </c>
       <c r="C894" t="n">
-        <v>707.214256391917</v>
+        <v>707.2142563919172</v>
       </c>
     </row>
     <row r="895">
@@ -10315,7 +10315,7 @@
         <v>956</v>
       </c>
       <c r="C899" t="n">
-        <v>852.5051694906689</v>
+        <v>852.5051694906688</v>
       </c>
     </row>
     <row r="900">
@@ -10359,7 +10359,7 @@
         <v>910</v>
       </c>
       <c r="C903" t="n">
-        <v>733.6316249199114</v>
+        <v>733.6316249199112</v>
       </c>
     </row>
     <row r="904">
@@ -10447,7 +10447,7 @@
         <v>1604</v>
       </c>
       <c r="C911" t="n">
-        <v>1487.337258780073</v>
+        <v>1487.337258780072</v>
       </c>
     </row>
     <row r="912">
@@ -10546,7 +10546,7 @@
         <v>166</v>
       </c>
       <c r="C920" t="n">
-        <v>177.7219580188479</v>
+        <v>177.721958018848</v>
       </c>
     </row>
     <row r="921">
@@ -10755,7 +10755,7 @@
         <v>848</v>
       </c>
       <c r="C939" t="n">
-        <v>937.6862360564621</v>
+        <v>937.6862360564622</v>
       </c>
     </row>
     <row r="940">
@@ -10766,7 +10766,7 @@
         <v>622</v>
       </c>
       <c r="C940" t="n">
-        <v>685.5377915364514</v>
+        <v>685.5377915364512</v>
       </c>
     </row>
     <row r="941">
@@ -10843,7 +10843,7 @@
         <v>172</v>
       </c>
       <c r="C947" t="n">
-        <v>171.7749473929382</v>
+        <v>171.7749473929381</v>
       </c>
     </row>
     <row r="948">
@@ -10865,7 +10865,7 @@
         <v>942</v>
       </c>
       <c r="C949" t="n">
-        <v>838.426538282283</v>
+        <v>838.4265382822831</v>
       </c>
     </row>
     <row r="950">
@@ -10887,7 +10887,7 @@
         <v>1262</v>
       </c>
       <c r="C951" t="n">
-        <v>1257.940989152562</v>
+        <v>1257.940989152561</v>
       </c>
     </row>
     <row r="952">
@@ -11030,7 +11030,7 @@
         <v>692</v>
       </c>
       <c r="C964" t="n">
-        <v>752.4042185214529</v>
+        <v>752.4042185214527</v>
       </c>
     </row>
     <row r="965">
@@ -11052,7 +11052,7 @@
         <v>491</v>
       </c>
       <c r="C966" t="n">
-        <v>459.500769510122</v>
+        <v>459.5007695101219</v>
       </c>
     </row>
     <row r="967">
@@ -11063,7 +11063,7 @@
         <v>335</v>
       </c>
       <c r="C967" t="n">
-        <v>344.9483151709685</v>
+        <v>344.9483151709684</v>
       </c>
     </row>
     <row r="968">
@@ -11118,7 +11118,7 @@
         <v>409</v>
       </c>
       <c r="C972" t="n">
-        <v>429.2747798906793</v>
+        <v>429.2747798906792</v>
       </c>
     </row>
     <row r="973">
@@ -11250,7 +11250,7 @@
         <v>1183</v>
       </c>
       <c r="C984" t="n">
-        <v>1180.38295716513</v>
+        <v>1180.382957165129</v>
       </c>
     </row>
     <row r="985">
@@ -11305,7 +11305,7 @@
         <v>708</v>
       </c>
       <c r="C989" t="n">
-        <v>707.2564789592305</v>
+        <v>707.2564789592304</v>
       </c>
     </row>
     <row r="990">
@@ -11327,7 +11327,7 @@
         <v>466</v>
       </c>
       <c r="C991" t="n">
-        <v>430.6890257915197</v>
+        <v>430.6890257915196</v>
       </c>
     </row>
     <row r="992">
@@ -11635,7 +11635,7 @@
         <v>792</v>
       </c>
       <c r="C1019" t="n">
-        <v>806.1580130723642</v>
+        <v>806.1580130723639</v>
       </c>
     </row>
     <row r="1020">
@@ -11657,7 +11657,7 @@
         <v>800</v>
       </c>
       <c r="C1021" t="n">
-        <v>653.9807631196692</v>
+        <v>653.9807631196691</v>
       </c>
     </row>
     <row r="1022">
@@ -11668,7 +11668,7 @@
         <v>764</v>
       </c>
       <c r="C1022" t="n">
-        <v>736.8302991726423</v>
+        <v>736.8302991726421</v>
       </c>
     </row>
     <row r="1023">
@@ -11723,7 +11723,7 @@
         <v>1463</v>
       </c>
       <c r="C1027" t="n">
-        <v>837.3013594094482</v>
+        <v>837.3013594094483</v>
       </c>
     </row>
     <row r="1028">
@@ -11899,7 +11899,7 @@
         <v>192</v>
       </c>
       <c r="C1043" t="n">
-        <v>181.4864236339814</v>
+        <v>181.4864236339815</v>
       </c>
     </row>
     <row r="1044">
@@ -11910,7 +11910,7 @@
         <v>538</v>
       </c>
       <c r="C1044" t="n">
-        <v>399.9875931476435</v>
+        <v>399.9875931476436</v>
       </c>
     </row>
     <row r="1045">
@@ -11998,7 +11998,7 @@
         <v>1172</v>
       </c>
       <c r="C1052" t="n">
-        <v>1168.046027135745</v>
+        <v>1168.046027135746</v>
       </c>
     </row>
     <row r="1053">
@@ -12031,7 +12031,7 @@
         <v>1156</v>
       </c>
       <c r="C1055" t="n">
-        <v>1114.592010922573</v>
+        <v>1114.592010922574</v>
       </c>
     </row>
     <row r="1056">
@@ -12042,7 +12042,7 @@
         <v>1173</v>
       </c>
       <c r="C1056" t="n">
-        <v>1147.155221658535</v>
+        <v>1147.155221658536</v>
       </c>
     </row>
     <row r="1057">
@@ -12075,7 +12075,7 @@
         <v>878</v>
       </c>
       <c r="C1059" t="n">
-        <v>890.6134683757974</v>
+        <v>890.6134683757972</v>
       </c>
     </row>
     <row r="1060">
@@ -12086,7 +12086,7 @@
         <v>654</v>
       </c>
       <c r="C1060" t="n">
-        <v>703.478480870207</v>
+        <v>703.4784808702068</v>
       </c>
     </row>
     <row r="1061">
@@ -12097,7 +12097,7 @@
         <v>520</v>
       </c>
       <c r="C1061" t="n">
-        <v>555.1528554156735</v>
+        <v>555.1528554156736</v>
       </c>
     </row>
     <row r="1062">
@@ -12152,7 +12152,7 @@
         <v>121</v>
       </c>
       <c r="C1066" t="n">
-        <v>121.7693653411501</v>
+        <v>121.76936534115</v>
       </c>
     </row>
     <row r="1067">
@@ -12240,7 +12240,7 @@
         <v>1158</v>
       </c>
       <c r="C1074" t="n">
-        <v>1172.785793465747</v>
+        <v>1172.785793465748</v>
       </c>
     </row>
     <row r="1075">
@@ -12361,7 +12361,7 @@
         <v>794</v>
       </c>
       <c r="C1085" t="n">
-        <v>615.471303375242</v>
+        <v>615.4713033752419</v>
       </c>
     </row>
     <row r="1086">
@@ -12372,7 +12372,7 @@
         <v>580</v>
       </c>
       <c r="C1086" t="n">
-        <v>569.3699410840197</v>
+        <v>569.3699410840198</v>
       </c>
     </row>
     <row r="1087">
@@ -12383,7 +12383,7 @@
         <v>324</v>
       </c>
       <c r="C1087" t="n">
-        <v>333.5186644590033</v>
+        <v>333.5186644590034</v>
       </c>
     </row>
     <row r="1088">
@@ -12405,7 +12405,7 @@
         <v>163</v>
       </c>
       <c r="C1089" t="n">
-        <v>182.2308073081472</v>
+        <v>182.2308073081471</v>
       </c>
     </row>
     <row r="1090">
@@ -12614,7 +12614,7 @@
         <v>818</v>
       </c>
       <c r="C1108" t="n">
-        <v>877.6391290405388</v>
+        <v>877.6391290405387</v>
       </c>
     </row>
     <row r="1109">
@@ -12625,7 +12625,7 @@
         <v>728</v>
       </c>
       <c r="C1109" t="n">
-        <v>713.0527204796853</v>
+        <v>713.0527204796854</v>
       </c>
     </row>
     <row r="1110">
@@ -12636,7 +12636,7 @@
         <v>632</v>
       </c>
       <c r="C1110" t="n">
-        <v>606.7157768521637</v>
+        <v>606.7157768521636</v>
       </c>
     </row>
     <row r="1111">
@@ -12977,7 +12977,7 @@
         <v>870</v>
       </c>
       <c r="C1141" t="n">
-        <v>730.0423235232836</v>
+        <v>730.0423235232837</v>
       </c>
     </row>
     <row r="1142">
@@ -12999,7 +12999,7 @@
         <v>874</v>
       </c>
       <c r="C1143" t="n">
-        <v>733.9967422456987</v>
+        <v>733.9967422456986</v>
       </c>
     </row>
     <row r="1144">
@@ -13010,7 +13010,7 @@
         <v>1124</v>
       </c>
       <c r="C1144" t="n">
-        <v>860.92153348378</v>
+        <v>860.9215334837801</v>
       </c>
     </row>
     <row r="1145">
@@ -13087,7 +13087,7 @@
         <v>1640</v>
       </c>
       <c r="C1151" t="n">
-        <v>1508.834638552304</v>
+        <v>1508.834638552305</v>
       </c>
     </row>
     <row r="1152">
@@ -13142,7 +13142,7 @@
         <v>1386</v>
       </c>
       <c r="C1156" t="n">
-        <v>1465.390612100758</v>
+        <v>1465.390612100757</v>
       </c>
     </row>
     <row r="1157">
@@ -13164,7 +13164,7 @@
         <v>1026</v>
       </c>
       <c r="C1158" t="n">
-        <v>999.9010710179733</v>
+        <v>999.9010710179734</v>
       </c>
     </row>
     <row r="1159">
@@ -13175,7 +13175,7 @@
         <v>245</v>
       </c>
       <c r="C1159" t="n">
-        <v>420.9518894011713</v>
+        <v>420.9518894011715</v>
       </c>
     </row>
     <row r="1160">
@@ -13186,7 +13186,7 @@
         <v>158</v>
       </c>
       <c r="C1160" t="n">
-        <v>178.2762448273118</v>
+        <v>178.2762448273119</v>
       </c>
     </row>
     <row r="1161">
@@ -13208,7 +13208,7 @@
         <v>116</v>
       </c>
       <c r="C1162" t="n">
-        <v>121.1296891106997</v>
+        <v>121.1296891106998</v>
       </c>
     </row>
     <row r="1163">
@@ -13241,7 +13241,7 @@
         <v>912</v>
       </c>
       <c r="C1165" t="n">
-        <v>821.0727029178174</v>
+        <v>821.0727029178172</v>
       </c>
     </row>
     <row r="1166">
@@ -13406,7 +13406,7 @@
         <v>666</v>
       </c>
       <c r="C1180" t="n">
-        <v>703.8452403503921</v>
+        <v>703.845240350392</v>
       </c>
     </row>
     <row r="1181">
@@ -13428,7 +13428,7 @@
         <v>416</v>
       </c>
       <c r="C1182" t="n">
-        <v>371.0209079330053</v>
+        <v>371.0209079330052</v>
       </c>
     </row>
     <row r="1183">
@@ -13494,7 +13494,7 @@
         <v>434</v>
       </c>
       <c r="C1188" t="n">
-        <v>412.9922969934703</v>
+        <v>412.9922969934702</v>
       </c>
     </row>
     <row r="1189">
@@ -13516,7 +13516,7 @@
         <v>1561</v>
       </c>
       <c r="C1190" t="n">
-        <v>1441.852340004287</v>
+        <v>1441.852340004286</v>
       </c>
     </row>
     <row r="1191">
@@ -13604,7 +13604,7 @@
         <v>1192</v>
       </c>
       <c r="C1198" t="n">
-        <v>1129.572218583676</v>
+        <v>1129.572218583675</v>
       </c>
     </row>
     <row r="1199">
@@ -13648,7 +13648,7 @@
         <v>1158</v>
       </c>
       <c r="C1202" t="n">
-        <v>1219.005391004051</v>
+        <v>1219.00539100405</v>
       </c>
     </row>
     <row r="1203">
@@ -13780,7 +13780,7 @@
         <v>1558</v>
       </c>
       <c r="C1214" t="n">
-        <v>1259.88394153602</v>
+        <v>1259.883941536021</v>
       </c>
     </row>
     <row r="1215">
@@ -13846,7 +13846,7 @@
         <v>1241</v>
       </c>
       <c r="C1220" t="n">
-        <v>1252.896806477019</v>
+        <v>1252.89680647702</v>
       </c>
     </row>
     <row r="1221">
@@ -13890,7 +13890,7 @@
         <v>1180</v>
       </c>
       <c r="C1224" t="n">
-        <v>1176.500300595526</v>
+        <v>1176.500300595527</v>
       </c>
     </row>
     <row r="1225">
@@ -14077,7 +14077,7 @@
         <v>1235</v>
       </c>
       <c r="C1241" t="n">
-        <v>1251.327389828727</v>
+        <v>1251.327389828726</v>
       </c>
     </row>
     <row r="1242">
@@ -14088,7 +14088,7 @@
         <v>1250</v>
       </c>
       <c r="C1242" t="n">
-        <v>1262.494060565154</v>
+        <v>1262.494060565153</v>
       </c>
     </row>
     <row r="1243">
@@ -14132,7 +14132,7 @@
         <v>1130</v>
       </c>
       <c r="C1246" t="n">
-        <v>1159.855815406359</v>
+        <v>1159.85581540636</v>
       </c>
     </row>
     <row r="1247">
@@ -14143,7 +14143,7 @@
         <v>1128</v>
       </c>
       <c r="C1247" t="n">
-        <v>1107.842374248513</v>
+        <v>1107.842374248512</v>
       </c>
     </row>
     <row r="1248">
@@ -14220,7 +14220,7 @@
         <v>791</v>
       </c>
       <c r="C1254" t="n">
-        <v>696.2279119156738</v>
+        <v>696.2279119156736</v>
       </c>
     </row>
     <row r="1255">
@@ -14264,7 +14264,7 @@
         <v>990</v>
       </c>
       <c r="C1258" t="n">
-        <v>829.3395415930936</v>
+        <v>829.3395415930935</v>
       </c>
     </row>
     <row r="1259">
@@ -14275,7 +14275,7 @@
         <v>840</v>
       </c>
       <c r="C1259" t="n">
-        <v>640.6400509160192</v>
+        <v>640.640050916019</v>
       </c>
     </row>
     <row r="1260">
@@ -14286,7 +14286,7 @@
         <v>820</v>
       </c>
       <c r="C1260" t="n">
-        <v>652.9569411348674</v>
+        <v>652.9569411348673</v>
       </c>
     </row>
     <row r="1261">
@@ -14319,7 +14319,7 @@
         <v>902</v>
       </c>
       <c r="C1263" t="n">
-        <v>746.8039611468085</v>
+        <v>746.8039611468084</v>
       </c>
     </row>
     <row r="1264">
@@ -14330,7 +14330,7 @@
         <v>1139</v>
       </c>
       <c r="C1264" t="n">
-        <v>942.9243355415997</v>
+        <v>942.9243355415996</v>
       </c>
     </row>
     <row r="1265">
@@ -14385,7 +14385,7 @@
         <v>1473</v>
       </c>
       <c r="C1269" t="n">
-        <v>1623.483517642694</v>
+        <v>1623.483517642693</v>
       </c>
     </row>
     <row r="1270">
@@ -14506,7 +14506,7 @@
         <v>156</v>
       </c>
       <c r="C1280" t="n">
-        <v>174.2504203643293</v>
+        <v>174.2504203643292</v>
       </c>
     </row>
     <row r="1281">
@@ -14539,7 +14539,7 @@
         <v>201</v>
       </c>
       <c r="C1283" t="n">
-        <v>183.2821219023194</v>
+        <v>183.2821219023195</v>
       </c>
     </row>
     <row r="1284">
@@ -14561,7 +14561,7 @@
         <v>928</v>
       </c>
       <c r="C1285" t="n">
-        <v>834.5800265856773</v>
+        <v>834.5800265856774</v>
       </c>
     </row>
     <row r="1286">
@@ -14715,7 +14715,7 @@
         <v>847</v>
       </c>
       <c r="C1299" t="n">
-        <v>847.3326814391462</v>
+        <v>847.3326814391461</v>
       </c>
     </row>
     <row r="1300">
@@ -14726,7 +14726,7 @@
         <v>662</v>
       </c>
       <c r="C1300" t="n">
-        <v>681.8735969741502</v>
+        <v>681.8735969741505</v>
       </c>
     </row>
     <row r="1301">
@@ -14803,7 +14803,7 @@
         <v>178</v>
       </c>
       <c r="C1307" t="n">
-        <v>181.3942513505717</v>
+        <v>181.3942513505716</v>
       </c>
     </row>
     <row r="1308">
@@ -15023,7 +15023,7 @@
         <v>1024</v>
       </c>
       <c r="C1327" t="n">
-        <v>348.730307554424</v>
+        <v>348.7303075544239</v>
       </c>
     </row>
     <row r="1328">
@@ -15056,7 +15056,7 @@
         <v>462</v>
       </c>
       <c r="C1330" t="n">
-        <v>404.876693610906</v>
+        <v>404.8766936109061</v>
       </c>
     </row>
     <row r="1331">
@@ -15067,7 +15067,7 @@
         <v>428</v>
       </c>
       <c r="C1331" t="n">
-        <v>313.1122980690529</v>
+        <v>313.112298069053</v>
       </c>
     </row>
     <row r="1332">
@@ -15078,7 +15078,7 @@
         <v>558</v>
       </c>
       <c r="C1332" t="n">
-        <v>346.5862752879633</v>
+        <v>346.5862752879632</v>
       </c>
     </row>
     <row r="1333">
@@ -15254,7 +15254,7 @@
         <v>1776</v>
       </c>
       <c r="C1348" t="n">
-        <v>1410.144165320924</v>
+        <v>1410.144165320923</v>
       </c>
     </row>
     <row r="1349">
@@ -15331,7 +15331,7 @@
         <v>758</v>
       </c>
       <c r="C1355" t="n">
-        <v>599.5527763580772</v>
+        <v>599.5527763580773</v>
       </c>
     </row>
     <row r="1356">
@@ -15375,7 +15375,7 @@
         <v>868</v>
       </c>
       <c r="C1359" t="n">
-        <v>721.237616543669</v>
+        <v>721.2376165436691</v>
       </c>
     </row>
     <row r="1360">
@@ -15441,7 +15441,7 @@
         <v>1749</v>
       </c>
       <c r="C1365" t="n">
-        <v>1664.875427110426</v>
+        <v>1664.875427110427</v>
       </c>
     </row>
     <row r="1366">
@@ -15573,7 +15573,7 @@
         <v>463</v>
       </c>
       <c r="C1377" t="n">
-        <v>329.1897351862271</v>
+        <v>329.1897351862272</v>
       </c>
     </row>
     <row r="1378">
@@ -15694,7 +15694,7 @@
         <v>1033</v>
       </c>
       <c r="C1388" t="n">
-        <v>987.9930802718171</v>
+        <v>987.9930802718173</v>
       </c>
     </row>
     <row r="1389">
@@ -15716,7 +15716,7 @@
         <v>1219</v>
       </c>
       <c r="C1390" t="n">
-        <v>867.9630803511895</v>
+        <v>867.9630803511894</v>
       </c>
     </row>
     <row r="1391">
@@ -15738,7 +15738,7 @@
         <v>893</v>
       </c>
       <c r="C1392" t="n">
-        <v>1132.114816756888</v>
+        <v>1132.114816756887</v>
       </c>
     </row>
     <row r="1393">
@@ -15749,7 +15749,7 @@
         <v>802</v>
       </c>
       <c r="C1393" t="n">
-        <v>947.4614744381698</v>
+        <v>947.4614744381699</v>
       </c>
     </row>
     <row r="1394">
@@ -15793,7 +15793,7 @@
         <v>480</v>
       </c>
       <c r="C1397" t="n">
-        <v>509.6923639626418</v>
+        <v>509.6923639626417</v>
       </c>
     </row>
     <row r="1398">
@@ -15947,7 +15947,7 @@
         <v>439</v>
       </c>
       <c r="C1411" t="n">
-        <v>986.0556084232088</v>
+        <v>986.0556084232086</v>
       </c>
     </row>
     <row r="1412">
@@ -15958,7 +15958,7 @@
         <v>1184</v>
       </c>
       <c r="C1412" t="n">
-        <v>991.9438814802471</v>
+        <v>991.9438814802472</v>
       </c>
     </row>
     <row r="1413">
@@ -15991,7 +15991,7 @@
         <v>1149</v>
       </c>
       <c r="C1415" t="n">
-        <v>1117.76936839662</v>
+        <v>1117.769368396619</v>
       </c>
     </row>
     <row r="1416">
@@ -16046,7 +16046,7 @@
         <v>672</v>
       </c>
       <c r="C1420" t="n">
-        <v>718.4061324391914</v>
+        <v>718.4061324391915</v>
       </c>
     </row>
     <row r="1421">
@@ -16090,7 +16090,7 @@
         <v>892</v>
       </c>
       <c r="C1424" t="n">
-        <v>467.1306170325587</v>
+        <v>467.1306170325586</v>
       </c>
     </row>
     <row r="1425">
@@ -16134,7 +16134,7 @@
         <v>959</v>
       </c>
       <c r="C1428" t="n">
-        <v>527.2266105518055</v>
+        <v>527.2266105518056</v>
       </c>
     </row>
     <row r="1429">
@@ -16156,7 +16156,7 @@
         <v>1544</v>
       </c>
       <c r="C1430" t="n">
-        <v>1289.571624424281</v>
+        <v>1289.57162442428</v>
       </c>
     </row>
     <row r="1431">
@@ -16233,7 +16233,7 @@
         <v>1036</v>
       </c>
       <c r="C1437" t="n">
-        <v>1164.34255760882</v>
+        <v>1164.342557608821</v>
       </c>
     </row>
     <row r="1438">
@@ -16255,7 +16255,7 @@
         <v>801</v>
       </c>
       <c r="C1439" t="n">
-        <v>959.6094616788855</v>
+        <v>959.6094616788854</v>
       </c>
     </row>
     <row r="1440">
@@ -16266,7 +16266,7 @@
         <v>714</v>
       </c>
       <c r="C1440" t="n">
-        <v>949.3681756727326</v>
+        <v>949.3681756727327</v>
       </c>
     </row>
     <row r="1441">
@@ -16332,7 +16332,7 @@
         <v>580</v>
       </c>
       <c r="C1446" t="n">
-        <v>448.0658793580195</v>
+        <v>448.0658793580196</v>
       </c>
     </row>
     <row r="1447">
@@ -16365,7 +16365,7 @@
         <v>192</v>
       </c>
       <c r="C1449" t="n">
-        <v>206.37832789063</v>
+        <v>206.3783278906301</v>
       </c>
     </row>
     <row r="1450">
@@ -16398,7 +16398,7 @@
         <v>444</v>
       </c>
       <c r="C1452" t="n">
-        <v>425.7272116434595</v>
+        <v>425.7272116434596</v>
       </c>
     </row>
     <row r="1453">
@@ -16409,7 +16409,7 @@
         <v>1082</v>
       </c>
       <c r="C1453" t="n">
-        <v>841.8615235458935</v>
+        <v>841.8615235458938</v>
       </c>
     </row>
     <row r="1454">
@@ -16420,7 +16420,7 @@
         <v>1527</v>
       </c>
       <c r="C1454" t="n">
-        <v>1222.145878598921</v>
+        <v>1222.145878598922</v>
       </c>
     </row>
     <row r="1455">
@@ -16497,7 +16497,7 @@
         <v>504</v>
       </c>
       <c r="C1461" t="n">
-        <v>995.8814160241435</v>
+        <v>995.8814160241437</v>
       </c>
     </row>
     <row r="1462">
@@ -16519,7 +16519,7 @@
         <v>1300</v>
       </c>
       <c r="C1463" t="n">
-        <v>973.9899396650632</v>
+        <v>973.989939665063</v>
       </c>
     </row>
     <row r="1464">
@@ -16596,7 +16596,7 @@
         <v>602</v>
       </c>
       <c r="C1470" t="n">
-        <v>654.2643954511448</v>
+        <v>654.2643954511449</v>
       </c>
     </row>
     <row r="1471">
@@ -16640,7 +16640,7 @@
         <v>974</v>
       </c>
       <c r="C1474" t="n">
-        <v>965.5012798630881</v>
+        <v>965.5012798630884</v>
       </c>
     </row>
     <row r="1475">
@@ -16651,7 +16651,7 @@
         <v>960</v>
       </c>
       <c r="C1475" t="n">
-        <v>759.8053628791981</v>
+        <v>759.8053628791982</v>
       </c>
     </row>
     <row r="1476">
@@ -16684,7 +16684,7 @@
         <v>768</v>
       </c>
       <c r="C1478" t="n">
-        <v>718.5608529783932</v>
+        <v>718.5608529783934</v>
       </c>
     </row>
     <row r="1479">
@@ -16761,7 +16761,7 @@
         <v>1849</v>
       </c>
       <c r="C1485" t="n">
-        <v>1697.66367207489</v>
+        <v>1697.663672074889</v>
       </c>
     </row>
     <row r="1486">
@@ -16926,7 +16926,7 @@
         <v>444</v>
       </c>
       <c r="C1500" t="n">
-        <v>425.8081168083272</v>
+        <v>425.8081168083273</v>
       </c>
     </row>
     <row r="1501">
@@ -17003,7 +17003,7 @@
         <v>474</v>
       </c>
       <c r="C1507" t="n">
-        <v>980.5253105888303</v>
+        <v>980.5253105888302</v>
       </c>
     </row>
     <row r="1508">
@@ -17113,7 +17113,7 @@
         <v>812</v>
       </c>
       <c r="C1517" t="n">
-        <v>646.935316103412</v>
+        <v>646.9353161034119</v>
       </c>
     </row>
     <row r="1518">
@@ -17124,7 +17124,7 @@
         <v>602</v>
       </c>
       <c r="C1518" t="n">
-        <v>635.1149326623167</v>
+        <v>635.1149326623168</v>
       </c>
     </row>
     <row r="1519">
@@ -17179,7 +17179,7 @@
         <v>188</v>
       </c>
       <c r="C1523" t="n">
-        <v>187.2824303968743</v>
+        <v>187.2824303968744</v>
       </c>
     </row>
     <row r="1524">
@@ -17190,7 +17190,7 @@
         <v>487</v>
       </c>
       <c r="C1524" t="n">
-        <v>399.4093778444322</v>
+        <v>399.4093778444323</v>
       </c>
     </row>
     <row r="1525">
@@ -17201,7 +17201,7 @@
         <v>926</v>
       </c>
       <c r="C1525" t="n">
-        <v>820.3784975780268</v>
+        <v>820.3784975780266</v>
       </c>
     </row>
     <row r="1526">
@@ -17344,7 +17344,7 @@
         <v>1058</v>
       </c>
       <c r="C1538" t="n">
-        <v>1121.306133209734</v>
+        <v>1121.306133209735</v>
       </c>
     </row>
     <row r="1539">
@@ -17355,7 +17355,7 @@
         <v>886</v>
       </c>
       <c r="C1539" t="n">
-        <v>984.7101936642564</v>
+        <v>984.7101936642562</v>
       </c>
     </row>
     <row r="1540">
@@ -17366,7 +17366,7 @@
         <v>664</v>
       </c>
       <c r="C1540" t="n">
-        <v>718.3718455808128</v>
+        <v>718.371845580813</v>
       </c>
     </row>
     <row r="1541">
@@ -17465,7 +17465,7 @@
         <v>912</v>
       </c>
       <c r="C1549" t="n">
-        <v>849.2412054689115</v>
+        <v>849.2412054689116</v>
       </c>
     </row>
     <row r="1550">
@@ -17608,7 +17608,7 @@
         <v>1136</v>
       </c>
       <c r="C1562" t="n">
-        <v>1154.153528483789</v>
+        <v>1154.15352848379</v>
       </c>
     </row>
     <row r="1563">
@@ -17641,7 +17641,7 @@
         <v>651</v>
       </c>
       <c r="C1565" t="n">
-        <v>688.298333221225</v>
+        <v>688.2983332212252</v>
       </c>
     </row>
     <row r="1566">
@@ -17674,7 +17674,7 @@
         <v>254</v>
       </c>
       <c r="C1568" t="n">
-        <v>316.3328721627481</v>
+        <v>316.3328721627482</v>
       </c>
     </row>
     <row r="1569">
@@ -17751,7 +17751,7 @@
         <v>1253</v>
       </c>
       <c r="C1575" t="n">
-        <v>1157.383086625071</v>
+        <v>1157.383086625072</v>
       </c>
     </row>
     <row r="1576">
@@ -17905,7 +17905,7 @@
         <v>809</v>
       </c>
       <c r="C1589" t="n">
-        <v>796.4989923846412</v>
+        <v>796.4989923846413</v>
       </c>
     </row>
     <row r="1590">
@@ -17916,7 +17916,7 @@
         <v>780</v>
       </c>
       <c r="C1590" t="n">
-        <v>719.7441846244127</v>
+        <v>719.7441846244129</v>
       </c>
     </row>
     <row r="1591">
@@ -17993,7 +17993,7 @@
         <v>1089</v>
       </c>
       <c r="C1597" t="n">
-        <v>758.5147597488582</v>
+        <v>758.5147597488581</v>
       </c>
     </row>
     <row r="1598">
@@ -18004,7 +18004,7 @@
         <v>948</v>
       </c>
       <c r="C1598" t="n">
-        <v>728.5604037865835</v>
+        <v>728.5604037865834</v>
       </c>
     </row>
     <row r="1599">
@@ -18015,7 +18015,7 @@
         <v>706</v>
       </c>
       <c r="C1599" t="n">
-        <v>807.2392527560228</v>
+        <v>807.2392527560227</v>
       </c>
     </row>
     <row r="1600">
@@ -18037,7 +18037,7 @@
         <v>356</v>
       </c>
       <c r="C1601" t="n">
-        <v>607.2807006368405</v>
+        <v>607.2807006368406</v>
       </c>
     </row>
     <row r="1602">
@@ -18070,7 +18070,7 @@
         <v>1958</v>
       </c>
       <c r="C1604" t="n">
-        <v>1694.862863428915</v>
+        <v>1694.862863428916</v>
       </c>
     </row>
     <row r="1605">
@@ -18081,7 +18081,7 @@
         <v>1800</v>
       </c>
       <c r="C1605" t="n">
-        <v>1715.266388333527</v>
+        <v>1715.266388333528</v>
       </c>
     </row>
     <row r="1606">
@@ -18147,7 +18147,7 @@
         <v>1508</v>
       </c>
       <c r="C1611" t="n">
-        <v>1506.530892732974</v>
+        <v>1506.530892732975</v>
       </c>
     </row>
     <row r="1612">
@@ -18180,7 +18180,7 @@
         <v>966</v>
       </c>
       <c r="C1614" t="n">
-        <v>919.1669825988373</v>
+        <v>919.1669825988375</v>
       </c>
     </row>
     <row r="1615">
@@ -18444,7 +18444,7 @@
         <v>390</v>
       </c>
       <c r="C1638" t="n">
-        <v>390.6347794641838</v>
+        <v>390.6347794641837</v>
       </c>
     </row>
     <row r="1639">
@@ -18477,7 +18477,7 @@
         <v>124</v>
       </c>
       <c r="C1641" t="n">
-        <v>121.9984549531832</v>
+        <v>121.9984549531831</v>
       </c>
     </row>
     <row r="1642">
@@ -18488,7 +18488,7 @@
         <v>133</v>
       </c>
       <c r="C1642" t="n">
-        <v>122.838054418842</v>
+        <v>122.8380544188419</v>
       </c>
     </row>
     <row r="1643">
@@ -18499,7 +18499,7 @@
         <v>180</v>
       </c>
       <c r="C1643" t="n">
-        <v>183.1138017523662</v>
+        <v>183.1138017523663</v>
       </c>
     </row>
     <row r="1644">
@@ -18510,7 +18510,7 @@
         <v>392</v>
       </c>
       <c r="C1644" t="n">
-        <v>397.5070873932588</v>
+        <v>397.5070873932587</v>
       </c>
     </row>
     <row r="1645">
@@ -18521,7 +18521,7 @@
         <v>876</v>
       </c>
       <c r="C1645" t="n">
-        <v>815.8551188518851</v>
+        <v>815.8551188518852</v>
       </c>
     </row>
     <row r="1646">
@@ -18675,7 +18675,7 @@
         <v>876</v>
       </c>
       <c r="C1659" t="n">
-        <v>979.5417398465173</v>
+        <v>979.5417398465172</v>
       </c>
     </row>
     <row r="1660">
@@ -18719,7 +18719,7 @@
         <v>272</v>
       </c>
       <c r="C1663" t="n">
-        <v>344.8830755774201</v>
+        <v>344.8830755774202</v>
       </c>
     </row>
     <row r="1664">
@@ -18829,7 +18829,7 @@
         <v>1128</v>
       </c>
       <c r="C1673" t="n">
-        <v>1154.522263402748</v>
+        <v>1154.522263402749</v>
       </c>
     </row>
     <row r="1674">
@@ -18906,7 +18906,7 @@
         <v>1174</v>
       </c>
       <c r="C1680" t="n">
-        <v>1145.570764617307</v>
+        <v>1145.570764617308</v>
       </c>
     </row>
     <row r="1681">
@@ -18950,7 +18950,7 @@
         <v>790</v>
       </c>
       <c r="C1684" t="n">
-        <v>816.9277317791726</v>
+        <v>816.9277317791725</v>
       </c>
     </row>
     <row r="1685">
@@ -18961,7 +18961,7 @@
         <v>676</v>
       </c>
       <c r="C1685" t="n">
-        <v>688.9514052181471</v>
+        <v>688.9514052181472</v>
       </c>
     </row>
     <row r="1686">
@@ -19060,7 +19060,7 @@
         <v>1495</v>
       </c>
       <c r="C1694" t="n">
-        <v>1199.71675032748</v>
+        <v>1199.716750327481</v>
       </c>
     </row>
     <row r="1695">
@@ -19280,7 +19280,7 @@
         <v>1064</v>
       </c>
       <c r="C1714" t="n">
-        <v>952.6147689894007</v>
+        <v>952.6147689894004</v>
       </c>
     </row>
     <row r="1715">
@@ -19291,7 +19291,7 @@
         <v>900</v>
       </c>
       <c r="C1715" t="n">
-        <v>865.1408451344723</v>
+        <v>865.1408451344722</v>
       </c>
     </row>
     <row r="1716">
@@ -19302,7 +19302,7 @@
         <v>860</v>
       </c>
       <c r="C1716" t="n">
-        <v>595.4548771097757</v>
+        <v>595.4548771097758</v>
       </c>
     </row>
     <row r="1717">
@@ -19335,7 +19335,7 @@
         <v>608</v>
       </c>
       <c r="C1719" t="n">
-        <v>780.3697588937649</v>
+        <v>780.3697588937652</v>
       </c>
     </row>
     <row r="1720">
@@ -19379,7 +19379,7 @@
         <v>1814</v>
       </c>
       <c r="C1723" t="n">
-        <v>1675.033498718026</v>
+        <v>1675.033498718027</v>
       </c>
     </row>
     <row r="1724">
@@ -19434,7 +19434,7 @@
         <v>1798</v>
       </c>
       <c r="C1728" t="n">
-        <v>1557.908783808014</v>
+        <v>1557.908783808015</v>
       </c>
     </row>
     <row r="1729">
@@ -19577,7 +19577,7 @@
         <v>880</v>
       </c>
       <c r="C1741" t="n">
-        <v>843.8649965708074</v>
+        <v>843.8649965708075</v>
       </c>
     </row>
     <row r="1742">
@@ -19588,7 +19588,7 @@
         <v>1546</v>
       </c>
       <c r="C1742" t="n">
-        <v>1455.772417160009</v>
+        <v>1455.772417160008</v>
       </c>
     </row>
     <row r="1743">
@@ -19753,7 +19753,7 @@
         <v>478</v>
       </c>
       <c r="C1757" t="n">
-        <v>566.2943387624879</v>
+        <v>566.294338762488</v>
       </c>
     </row>
     <row r="1758">
@@ -19841,7 +19841,7 @@
         <v>872</v>
       </c>
       <c r="C1765" t="n">
-        <v>829.1448792288248</v>
+        <v>829.1448792288251</v>
       </c>
     </row>
     <row r="1766">
@@ -19852,7 +19852,7 @@
         <v>1504</v>
       </c>
       <c r="C1766" t="n">
-        <v>1387.142070789342</v>
+        <v>1387.142070789343</v>
       </c>
     </row>
     <row r="1767">
@@ -20050,7 +20050,7 @@
         <v>192</v>
       </c>
       <c r="C1784" t="n">
-        <v>202.2542544724984</v>
+        <v>202.2542544724985</v>
       </c>
     </row>
     <row r="1785">
@@ -20149,7 +20149,7 @@
         <v>1114</v>
       </c>
       <c r="C1793" t="n">
-        <v>1170.058806424278</v>
+        <v>1170.058806424279</v>
       </c>
     </row>
     <row r="1794">
@@ -20281,7 +20281,7 @@
         <v>682</v>
       </c>
       <c r="C1805" t="n">
-        <v>686.5331367776379</v>
+        <v>686.533136777638</v>
       </c>
     </row>
     <row r="1806">
@@ -20292,7 +20292,7 @@
         <v>582</v>
       </c>
       <c r="C1806" t="n">
-        <v>587.9316857661411</v>
+        <v>587.9316857661412</v>
       </c>
     </row>
     <row r="1807">
@@ -20468,7 +20468,7 @@
         <v>1169</v>
       </c>
       <c r="C1822" t="n">
-        <v>1116.858949256363</v>
+        <v>1116.858949256362</v>
       </c>
     </row>
     <row r="1823">
@@ -20512,7 +20512,7 @@
         <v>1134</v>
       </c>
       <c r="C1826" t="n">
-        <v>1150.206260895248</v>
+        <v>1150.206260895247</v>
       </c>
     </row>
     <row r="1827">
@@ -20556,7 +20556,7 @@
         <v>812</v>
       </c>
       <c r="C1830" t="n">
-        <v>745.918207579422</v>
+        <v>745.9182075794222</v>
       </c>
     </row>
     <row r="1831">
@@ -20611,7 +20611,7 @@
         <v>1062</v>
       </c>
       <c r="C1835" t="n">
-        <v>873.1810663357402</v>
+        <v>873.1810663357401</v>
       </c>
     </row>
     <row r="1836">
@@ -20633,7 +20633,7 @@
         <v>850</v>
       </c>
       <c r="C1837" t="n">
-        <v>795.0078064538701</v>
+        <v>795.0078064538703</v>
       </c>
     </row>
     <row r="1838">
@@ -20655,7 +20655,7 @@
         <v>874</v>
       </c>
       <c r="C1839" t="n">
-        <v>754.0187744023585</v>
+        <v>754.0187744023586</v>
       </c>
     </row>
     <row r="1840">
@@ -20721,7 +20721,7 @@
         <v>1910</v>
       </c>
       <c r="C1845" t="n">
-        <v>1699.38938469167</v>
+        <v>1699.389384691671</v>
       </c>
     </row>
     <row r="1846">
@@ -20798,7 +20798,7 @@
         <v>1644</v>
       </c>
       <c r="C1852" t="n">
-        <v>1224.028183410368</v>
+        <v>1224.028183410367</v>
       </c>
     </row>
     <row r="1853">
@@ -20886,7 +20886,7 @@
         <v>537</v>
       </c>
       <c r="C1860" t="n">
-        <v>410.7990467511466</v>
+        <v>410.7990467511465</v>
       </c>
     </row>
     <row r="1861">
@@ -20996,7 +20996,7 @@
         <v>1144</v>
       </c>
       <c r="C1870" t="n">
-        <v>910.0011408313101</v>
+        <v>910.0011408313098</v>
       </c>
     </row>
     <row r="1871">
@@ -21128,7 +21128,7 @@
         <v>164</v>
       </c>
       <c r="C1882" t="n">
-        <v>189.9982249950648</v>
+        <v>189.9982249950647</v>
       </c>
     </row>
     <row r="1883">
@@ -21227,7 +21227,7 @@
         <v>880</v>
       </c>
       <c r="C1891" t="n">
-        <v>964.5216701694037</v>
+        <v>964.5216701694035</v>
       </c>
     </row>
     <row r="1892">
@@ -21238,7 +21238,7 @@
         <v>462</v>
       </c>
       <c r="C1892" t="n">
-        <v>956.5213865819237</v>
+        <v>956.5213865819238</v>
       </c>
     </row>
     <row r="1893">
@@ -21249,7 +21249,7 @@
         <v>1134</v>
       </c>
       <c r="C1893" t="n">
-        <v>999.9210330540956</v>
+        <v>999.9210330540958</v>
       </c>
     </row>
     <row r="1894">
@@ -21326,7 +21326,7 @@
         <v>798</v>
       </c>
       <c r="C1900" t="n">
-        <v>819.2656498979595</v>
+        <v>819.2656498979594</v>
       </c>
     </row>
     <row r="1901">
@@ -21348,7 +21348,7 @@
         <v>498</v>
       </c>
       <c r="C1902" t="n">
-        <v>484.8548185318932</v>
+        <v>484.8548185318931</v>
       </c>
     </row>
     <row r="1903">
@@ -21392,7 +21392,7 @@
         <v>161</v>
       </c>
       <c r="C1906" t="n">
-        <v>169.7187839121259</v>
+        <v>169.718783912126</v>
       </c>
     </row>
     <row r="1907">
@@ -21425,7 +21425,7 @@
         <v>848</v>
       </c>
       <c r="C1909" t="n">
-        <v>843.9875666671156</v>
+        <v>843.9875666671157</v>
       </c>
     </row>
     <row r="1910">
@@ -21656,7 +21656,7 @@
         <v>736</v>
       </c>
       <c r="C1930" t="n">
-        <v>851.3165190780607</v>
+        <v>851.3165190780605</v>
       </c>
     </row>
     <row r="1931">
@@ -21711,7 +21711,7 @@
         <v>746</v>
       </c>
       <c r="C1935" t="n">
-        <v>715.7840996492872</v>
+        <v>715.7840996492873</v>
       </c>
     </row>
     <row r="1936">
@@ -21788,7 +21788,7 @@
         <v>1586</v>
       </c>
       <c r="C1942" t="n">
-        <v>1517.415576470909</v>
+        <v>1517.415576470908</v>
       </c>
     </row>
     <row r="1943">
@@ -21898,7 +21898,7 @@
         <v>173</v>
       </c>
       <c r="C1952" t="n">
-        <v>200.4967830148931</v>
+        <v>200.496783014893</v>
       </c>
     </row>
     <row r="1953">
@@ -21931,7 +21931,7 @@
         <v>180</v>
       </c>
       <c r="C1955" t="n">
-        <v>181.0246225916445</v>
+        <v>181.0246225916444</v>
       </c>
     </row>
     <row r="1956">
@@ -22118,7 +22118,7 @@
         <v>686</v>
       </c>
       <c r="C1972" t="n">
-        <v>653.4117093516853</v>
+        <v>653.4117093516854</v>
       </c>
     </row>
     <row r="1973">
@@ -22316,7 +22316,7 @@
         <v>1148</v>
       </c>
       <c r="C1990" t="n">
-        <v>1152.165103625207</v>
+        <v>1152.165103625206</v>
       </c>
     </row>
     <row r="1991">
@@ -22327,7 +22327,7 @@
         <v>1182</v>
       </c>
       <c r="C1991" t="n">
-        <v>1149.551505709456</v>
+        <v>1149.551505709457</v>
       </c>
     </row>
     <row r="1992">
@@ -22360,7 +22360,7 @@
         <v>1132</v>
       </c>
       <c r="C1994" t="n">
-        <v>1155.298073390205</v>
+        <v>1155.298073390204</v>
       </c>
     </row>
     <row r="1995">
@@ -22393,7 +22393,7 @@
         <v>614</v>
       </c>
       <c r="C1997" t="n">
-        <v>663.5891411204285</v>
+        <v>663.5891411204287</v>
       </c>
     </row>
     <row r="1998">
@@ -22404,7 +22404,7 @@
         <v>514</v>
       </c>
       <c r="C1998" t="n">
-        <v>482.1716855433502</v>
+        <v>482.1716855433501</v>
       </c>
     </row>
     <row r="1999">
@@ -22437,7 +22437,7 @@
         <v>188</v>
       </c>
       <c r="C2001" t="n">
-        <v>201.5009575180999</v>
+        <v>201.5009575181</v>
       </c>
     </row>
     <row r="2002">
@@ -22481,7 +22481,7 @@
         <v>817</v>
       </c>
       <c r="C2005" t="n">
-        <v>849.4659485051823</v>
+        <v>849.4659485051825</v>
       </c>
     </row>
     <row r="2006">
@@ -22514,7 +22514,7 @@
         <v>1215</v>
       </c>
       <c r="C2008" t="n">
-        <v>1180.662060031229</v>
+        <v>1180.66206003123</v>
       </c>
     </row>
     <row r="2009">
@@ -22646,7 +22646,7 @@
         <v>905</v>
       </c>
       <c r="C2020" t="n">
-        <v>903.2257537015468</v>
+        <v>903.225753701547</v>
       </c>
     </row>
     <row r="2021">
@@ -22690,7 +22690,7 @@
         <v>338</v>
       </c>
       <c r="C2024" t="n">
-        <v>353.9262145291481</v>
+        <v>353.9262145291483</v>
       </c>
     </row>
     <row r="2025">
@@ -22866,7 +22866,7 @@
         <v>950</v>
       </c>
       <c r="C2040" t="n">
-        <v>962.422682748625</v>
+        <v>962.4226827486251</v>
       </c>
     </row>
     <row r="2041">
@@ -22877,7 +22877,7 @@
         <v>974</v>
       </c>
       <c r="C2041" t="n">
-        <v>968.0675571593014</v>
+        <v>968.0675571593013</v>
       </c>
     </row>
     <row r="2042">
@@ -22976,7 +22976,7 @@
         <v>1048</v>
       </c>
       <c r="C2050" t="n">
-        <v>1086.150369086679</v>
+        <v>1086.150369086678</v>
       </c>
     </row>
     <row r="2051">
@@ -22987,7 +22987,7 @@
         <v>902</v>
       </c>
       <c r="C2051" t="n">
-        <v>859.9982405196168</v>
+        <v>859.9982405196166</v>
       </c>
     </row>
     <row r="2052">
@@ -23009,7 +23009,7 @@
         <v>784</v>
       </c>
       <c r="C2053" t="n">
-        <v>746.2315362654191</v>
+        <v>746.231536265419</v>
       </c>
     </row>
     <row r="2054">
@@ -23020,7 +23020,7 @@
         <v>747</v>
       </c>
       <c r="C2054" t="n">
-        <v>714.9537287874913</v>
+        <v>714.9537287874914</v>
       </c>
     </row>
     <row r="2055">
@@ -23031,7 +23031,7 @@
         <v>770</v>
       </c>
       <c r="C2055" t="n">
-        <v>706.5858625740506</v>
+        <v>706.5858625740507</v>
       </c>
     </row>
     <row r="2056">
@@ -23097,7 +23097,7 @@
         <v>1838</v>
       </c>
       <c r="C2061" t="n">
-        <v>1699.428393407031</v>
+        <v>1699.428393407032</v>
       </c>
     </row>
     <row r="2062">
@@ -23108,7 +23108,7 @@
         <v>1749</v>
       </c>
       <c r="C2062" t="n">
-        <v>1586.850962210399</v>
+        <v>1586.8509622104</v>
       </c>
     </row>
     <row r="2063">
@@ -23306,7 +23306,7 @@
         <v>1154</v>
       </c>
       <c r="C2080" t="n">
-        <v>1173.244448433426</v>
+        <v>1173.244448433427</v>
       </c>
     </row>
     <row r="2081">
@@ -23350,7 +23350,7 @@
         <v>1041</v>
       </c>
       <c r="C2084" t="n">
-        <v>1026.585989008801</v>
+        <v>1026.5859890088</v>
       </c>
     </row>
     <row r="2085">
@@ -23361,7 +23361,7 @@
         <v>1090</v>
       </c>
       <c r="C2085" t="n">
-        <v>1033.570771880244</v>
+        <v>1033.570771880243</v>
       </c>
     </row>
     <row r="2086">
@@ -23427,7 +23427,7 @@
         <v>840</v>
       </c>
       <c r="C2091" t="n">
-        <v>861.2992334837825</v>
+        <v>861.2992334837822</v>
       </c>
     </row>
     <row r="2092">
@@ -23482,7 +23482,7 @@
         <v>184</v>
       </c>
       <c r="C2096" t="n">
-        <v>191.9892404743244</v>
+        <v>191.9892404743243</v>
       </c>
     </row>
     <row r="2097">
@@ -23515,7 +23515,7 @@
         <v>218</v>
       </c>
       <c r="C2099" t="n">
-        <v>195.7376445292564</v>
+        <v>195.7376445292565</v>
       </c>
     </row>
     <row r="2100">
@@ -23702,7 +23702,7 @@
         <v>808</v>
       </c>
       <c r="C2116" t="n">
-        <v>856.5098434836842</v>
+        <v>856.5098434836841</v>
       </c>
     </row>
     <row r="2117">
@@ -23735,7 +23735,7 @@
         <v>362</v>
       </c>
       <c r="C2119" t="n">
-        <v>411.049882989258</v>
+        <v>411.0498829892581</v>
       </c>
     </row>
     <row r="2120">
@@ -23801,7 +23801,7 @@
         <v>967</v>
       </c>
       <c r="C2125" t="n">
-        <v>839.795903443008</v>
+        <v>839.7959034430079</v>
       </c>
     </row>
     <row r="2126">
@@ -23823,7 +23823,7 @@
         <v>1222</v>
       </c>
       <c r="C2127" t="n">
-        <v>1158.099981115066</v>
+        <v>1158.099981115067</v>
       </c>
     </row>
     <row r="2128">
@@ -23955,7 +23955,7 @@
         <v>1159</v>
       </c>
       <c r="C2139" t="n">
-        <v>1132.979317747938</v>
+        <v>1132.979317747937</v>
       </c>
     </row>
     <row r="2140">
@@ -23988,7 +23988,7 @@
         <v>646</v>
       </c>
       <c r="C2142" t="n">
-        <v>701.831424175571</v>
+        <v>701.8314241755711</v>
       </c>
     </row>
     <row r="2143">
@@ -24065,7 +24065,7 @@
         <v>1031</v>
       </c>
       <c r="C2149" t="n">
-        <v>815.365834406418</v>
+        <v>815.3658344064179</v>
       </c>
     </row>
     <row r="2150">
@@ -24164,7 +24164,7 @@
         <v>1102</v>
       </c>
       <c r="C2158" t="n">
-        <v>1132.110866566345</v>
+        <v>1132.110866566346</v>
       </c>
     </row>
     <row r="2159">
@@ -24219,7 +24219,7 @@
         <v>996</v>
       </c>
       <c r="C2163" t="n">
-        <v>1013.942051296528</v>
+        <v>1013.942051296527</v>
       </c>
     </row>
     <row r="2164">
@@ -24252,7 +24252,7 @@
         <v>766</v>
       </c>
       <c r="C2166" t="n">
-        <v>724.3551788813504</v>
+        <v>724.3551788813506</v>
       </c>
     </row>
     <row r="2167">
@@ -24296,7 +24296,7 @@
         <v>841</v>
       </c>
       <c r="C2170" t="n">
-        <v>859.5526482533168</v>
+        <v>859.5526482533165</v>
       </c>
     </row>
     <row r="2171">
@@ -24307,7 +24307,7 @@
         <v>740</v>
       </c>
       <c r="C2171" t="n">
-        <v>754.501779546261</v>
+        <v>754.5017795462611</v>
       </c>
     </row>
     <row r="2172">
@@ -24340,7 +24340,7 @@
         <v>813</v>
       </c>
       <c r="C2174" t="n">
-        <v>716.8194590760633</v>
+        <v>716.819459076063</v>
       </c>
     </row>
     <row r="2175">
@@ -24351,7 +24351,7 @@
         <v>742</v>
       </c>
       <c r="C2175" t="n">
-        <v>726.2094502969917</v>
+        <v>726.2094502969916</v>
       </c>
     </row>
     <row r="2176">
@@ -24582,7 +24582,7 @@
         <v>386</v>
       </c>
       <c r="C2196" t="n">
-        <v>389.9949636520211</v>
+        <v>389.9949636520212</v>
       </c>
     </row>
     <row r="2197">
@@ -24593,7 +24593,7 @@
         <v>822</v>
       </c>
       <c r="C2197" t="n">
-        <v>581.9217872044512</v>
+        <v>581.9217872044511</v>
       </c>
     </row>
     <row r="2198">
@@ -24670,7 +24670,7 @@
         <v>1072</v>
       </c>
       <c r="C2204" t="n">
-        <v>982.5292381222623</v>
+        <v>982.5292381222622</v>
       </c>
     </row>
     <row r="2205">
@@ -24780,7 +24780,7 @@
         <v>482</v>
       </c>
       <c r="C2214" t="n">
-        <v>467.528087987033</v>
+        <v>467.5280879870329</v>
       </c>
     </row>
     <row r="2215">
@@ -24846,7 +24846,7 @@
         <v>406</v>
       </c>
       <c r="C2220" t="n">
-        <v>351.6147026410761</v>
+        <v>351.6147026410762</v>
       </c>
     </row>
     <row r="2221">
@@ -24912,7 +24912,7 @@
         <v>1172</v>
       </c>
       <c r="C2226" t="n">
-        <v>1191.602029301583</v>
+        <v>1191.602029301582</v>
       </c>
     </row>
     <row r="2227">
@@ -24956,7 +24956,7 @@
         <v>1056</v>
       </c>
       <c r="C2230" t="n">
-        <v>862.0510949208931</v>
+        <v>862.0510949208933</v>
       </c>
     </row>
     <row r="2231">
@@ -25022,7 +25022,7 @@
         <v>1000</v>
       </c>
       <c r="C2236" t="n">
-        <v>692.5152603493455</v>
+        <v>692.5152603493453</v>
       </c>
     </row>
     <row r="2237">
@@ -25099,7 +25099,7 @@
         <v>184</v>
       </c>
       <c r="C2243" t="n">
-        <v>198.9574749732816</v>
+        <v>198.9574749732815</v>
       </c>
     </row>
     <row r="2244">
@@ -25275,7 +25275,7 @@
         <v>878</v>
       </c>
       <c r="C2259" t="n">
-        <v>886.4274302108446</v>
+        <v>886.4274302108447</v>
       </c>
     </row>
     <row r="2260">
@@ -25330,7 +25330,7 @@
         <v>299</v>
       </c>
       <c r="C2264" t="n">
-        <v>320.0265686572191</v>
+        <v>320.0265686572192</v>
       </c>
     </row>
     <row r="2265">
@@ -25363,7 +25363,7 @@
         <v>226</v>
       </c>
       <c r="C2267" t="n">
-        <v>210.3294375975598</v>
+        <v>210.3294375975597</v>
       </c>
     </row>
     <row r="2268">
@@ -25418,7 +25418,7 @@
         <v>1149</v>
       </c>
       <c r="C2272" t="n">
-        <v>1155.520478157705</v>
+        <v>1155.520478157704</v>
       </c>
     </row>
     <row r="2273">
@@ -25528,7 +25528,7 @@
         <v>963</v>
       </c>
       <c r="C2282" t="n">
-        <v>935.4709056762108</v>
+        <v>935.4709056762109</v>
       </c>
     </row>
     <row r="2283">
@@ -25550,7 +25550,7 @@
         <v>812</v>
       </c>
       <c r="C2284" t="n">
-        <v>820.3102884321561</v>
+        <v>820.3102884321562</v>
       </c>
     </row>
     <row r="2285">
@@ -25572,7 +25572,7 @@
         <v>730</v>
       </c>
       <c r="C2286" t="n">
-        <v>674.4370856989482</v>
+        <v>674.4370856989484</v>
       </c>
     </row>
     <row r="2287">
@@ -25616,7 +25616,7 @@
         <v>727</v>
       </c>
       <c r="C2290" t="n">
-        <v>732.5390297194998</v>
+        <v>732.5390297194999</v>
       </c>
     </row>
     <row r="2291">
@@ -25638,7 +25638,7 @@
         <v>600</v>
       </c>
       <c r="C2292" t="n">
-        <v>574.5886482947478</v>
+        <v>574.5886482947477</v>
       </c>
     </row>
     <row r="2293">
@@ -25671,7 +25671,7 @@
         <v>768</v>
       </c>
       <c r="C2295" t="n">
-        <v>670.2798302789596</v>
+        <v>670.2798302789597</v>
       </c>
     </row>
     <row r="2296">
@@ -25682,7 +25682,7 @@
         <v>960</v>
       </c>
       <c r="C2296" t="n">
-        <v>800.1897641863397</v>
+        <v>800.1897641863399</v>
       </c>
     </row>
     <row r="2297">
@@ -25693,7 +25693,7 @@
         <v>1321</v>
       </c>
       <c r="C2297" t="n">
-        <v>982.7458739942684</v>
+        <v>982.7458739942687</v>
       </c>
     </row>
     <row r="2298">
@@ -25748,7 +25748,7 @@
         <v>1602</v>
       </c>
       <c r="C2302" t="n">
-        <v>1503.202266804982</v>
+        <v>1503.202266804983</v>
       </c>
     </row>
     <row r="2303">
@@ -25781,7 +25781,7 @@
         <v>1750</v>
       </c>
       <c r="C2305" t="n">
-        <v>1556.192762313727</v>
+        <v>1556.192762313726</v>
       </c>
     </row>
     <row r="2306">
@@ -25814,7 +25814,7 @@
         <v>1582</v>
       </c>
       <c r="C2308" t="n">
-        <v>759.3226286720794</v>
+        <v>759.3226286720792</v>
       </c>
     </row>
     <row r="2309">
@@ -25913,7 +25913,7 @@
         <v>754</v>
       </c>
       <c r="C2317" t="n">
-        <v>573.1420426394531</v>
+        <v>573.1420426394529</v>
       </c>
     </row>
     <row r="2318">
@@ -25924,7 +25924,7 @@
         <v>1214</v>
       </c>
       <c r="C2318" t="n">
-        <v>912.6307631453953</v>
+        <v>912.6307631453955</v>
       </c>
     </row>
     <row r="2319">
@@ -25990,7 +25990,7 @@
         <v>1012</v>
       </c>
       <c r="C2324" t="n">
-        <v>937.2874177254348</v>
+        <v>937.2874177254349</v>
       </c>
     </row>
     <row r="2325">
@@ -26111,7 +26111,7 @@
         <v>307</v>
       </c>
       <c r="C2335" t="n">
-        <v>355.727267418018</v>
+        <v>355.7272674180178</v>
       </c>
     </row>
     <row r="2336">
@@ -26166,7 +26166,7 @@
         <v>402</v>
       </c>
       <c r="C2340" t="n">
-        <v>250.0989124515682</v>
+        <v>250.0989124515681</v>
       </c>
     </row>
     <row r="2341">
@@ -26276,7 +26276,7 @@
         <v>1044</v>
       </c>
       <c r="C2350" t="n">
-        <v>864.0647425392028</v>
+        <v>864.0647425392031</v>
       </c>
     </row>
     <row r="2351">
@@ -26298,7 +26298,7 @@
         <v>1026</v>
       </c>
       <c r="C2352" t="n">
-        <v>956.4191305726268</v>
+        <v>956.4191305726271</v>
       </c>
     </row>
     <row r="2353">
@@ -26309,7 +26309,7 @@
         <v>1063</v>
       </c>
       <c r="C2353" t="n">
-        <v>970.9443970429161</v>
+        <v>970.9443970429162</v>
       </c>
     </row>
     <row r="2354">
@@ -26342,7 +26342,7 @@
         <v>710</v>
       </c>
       <c r="C2356" t="n">
-        <v>716.7191106602633</v>
+        <v>716.7191106602634</v>
       </c>
     </row>
     <row r="2357">
@@ -26419,7 +26419,7 @@
         <v>185</v>
       </c>
       <c r="C2363" t="n">
-        <v>189.4443423356561</v>
+        <v>189.4443423356562</v>
       </c>
     </row>
     <row r="2364">
@@ -26507,7 +26507,7 @@
         <v>1114</v>
       </c>
       <c r="C2371" t="n">
-        <v>1116.344766912468</v>
+        <v>1116.344766912467</v>
       </c>
     </row>
     <row r="2372">
@@ -26606,7 +26606,7 @@
         <v>707</v>
       </c>
       <c r="C2380" t="n">
-        <v>758.0091915064913</v>
+        <v>758.009191506491</v>
       </c>
     </row>
     <row r="2381">
@@ -26617,7 +26617,7 @@
         <v>634</v>
       </c>
       <c r="C2381" t="n">
-        <v>665.3688338811113</v>
+        <v>665.3688338811112</v>
       </c>
     </row>
     <row r="2382">
@@ -26672,7 +26672,7 @@
         <v>188</v>
       </c>
       <c r="C2386" t="n">
-        <v>205.881402127832</v>
+        <v>205.8814021278321</v>
       </c>
     </row>
     <row r="2387">
@@ -26782,7 +26782,7 @@
         <v>966</v>
       </c>
       <c r="C2396" t="n">
-        <v>990.3154257827591</v>
+        <v>990.3154257827592</v>
       </c>
     </row>
     <row r="2397">
@@ -26815,7 +26815,7 @@
         <v>1063</v>
       </c>
       <c r="C2399" t="n">
-        <v>973.2713058727869</v>
+        <v>973.2713058727868</v>
       </c>
     </row>
     <row r="2400">
@@ -26881,7 +26881,7 @@
         <v>665</v>
       </c>
       <c r="C2405" t="n">
-        <v>694.6198741559085</v>
+        <v>694.6198741559083</v>
       </c>
     </row>
     <row r="2406">
@@ -26925,7 +26925,7 @@
         <v>888</v>
       </c>
       <c r="C2409" t="n">
-        <v>859.5239276222846</v>
+        <v>859.5239276222845</v>
       </c>
     </row>
     <row r="2410">
@@ -26947,7 +26947,7 @@
         <v>590</v>
       </c>
       <c r="C2411" t="n">
-        <v>705.4668183794295</v>
+        <v>705.4668183794294</v>
       </c>
     </row>
     <row r="2412">
@@ -27002,7 +27002,7 @@
         <v>1010</v>
       </c>
       <c r="C2416" t="n">
-        <v>833.0824549072845</v>
+        <v>833.0824549072844</v>
       </c>
     </row>
     <row r="2417">
@@ -27013,7 +27013,7 @@
         <v>1352</v>
       </c>
       <c r="C2417" t="n">
-        <v>1298.941529737227</v>
+        <v>1298.941529737228</v>
       </c>
     </row>
     <row r="2418">
@@ -27167,7 +27167,7 @@
         <v>202</v>
       </c>
       <c r="C2431" t="n">
-        <v>474.8904245697911</v>
+        <v>474.890424569791</v>
       </c>
     </row>
     <row r="2432">
@@ -27343,7 +27343,7 @@
         <v>1050</v>
       </c>
       <c r="C2447" t="n">
-        <v>1035.711238109059</v>
+        <v>1035.711238109058</v>
       </c>
     </row>
     <row r="2448">
@@ -27409,7 +27409,7 @@
         <v>490</v>
       </c>
       <c r="C2453" t="n">
-        <v>511.4577942197375</v>
+        <v>511.4577942197377</v>
       </c>
     </row>
     <row r="2454">
@@ -27420,7 +27420,7 @@
         <v>374</v>
       </c>
       <c r="C2454" t="n">
-        <v>352.0928422061645</v>
+        <v>352.0928422061646</v>
       </c>
     </row>
     <row r="2455">
@@ -27486,7 +27486,7 @@
         <v>476</v>
       </c>
       <c r="C2460" t="n">
-        <v>382.7491267513505</v>
+        <v>382.7491267513504</v>
       </c>
     </row>
     <row r="2461">
@@ -27497,7 +27497,7 @@
         <v>860</v>
       </c>
       <c r="C2461" t="n">
-        <v>772.5928142162602</v>
+        <v>772.5928142162603</v>
       </c>
     </row>
     <row r="2462">
@@ -27541,7 +27541,7 @@
         <v>1124</v>
       </c>
       <c r="C2465" t="n">
-        <v>1145.47643703283</v>
+        <v>1145.476437032831</v>
       </c>
     </row>
     <row r="2466">
@@ -27761,7 +27761,7 @@
         <v>856</v>
       </c>
       <c r="C2485" t="n">
-        <v>788.5249783301148</v>
+        <v>788.5249783301147</v>
       </c>
     </row>
     <row r="2486">
@@ -27827,7 +27827,7 @@
         <v>1132</v>
       </c>
       <c r="C2491" t="n">
-        <v>1144.847868254589</v>
+        <v>1144.84786825459</v>
       </c>
     </row>
     <row r="2492">
@@ -27937,7 +27937,7 @@
         <v>684</v>
       </c>
       <c r="C2501" t="n">
-        <v>715.9295970412219</v>
+        <v>715.929597041222</v>
       </c>
     </row>
     <row r="2502">
@@ -27981,7 +27981,7 @@
         <v>938</v>
       </c>
       <c r="C2505" t="n">
-        <v>983.1515160805012</v>
+        <v>983.1515160805013</v>
       </c>
     </row>
     <row r="2506">
@@ -28003,7 +28003,7 @@
         <v>720</v>
       </c>
       <c r="C2507" t="n">
-        <v>692.6437829633818</v>
+        <v>692.6437829633816</v>
       </c>
     </row>
     <row r="2508">
@@ -28025,7 +28025,7 @@
         <v>718</v>
       </c>
       <c r="C2509" t="n">
-        <v>708.6536449787122</v>
+        <v>708.6536449787124</v>
       </c>
     </row>
     <row r="2510">
@@ -28058,7 +28058,7 @@
         <v>890</v>
       </c>
       <c r="C2512" t="n">
-        <v>796.2114840203483</v>
+        <v>796.2114840203484</v>
       </c>
     </row>
     <row r="2513">
@@ -28091,7 +28091,7 @@
         <v>1596</v>
       </c>
       <c r="C2515" t="n">
-        <v>1479.395598900528</v>
+        <v>1479.395598900527</v>
       </c>
     </row>
     <row r="2516">
@@ -28289,7 +28289,7 @@
         <v>763</v>
       </c>
       <c r="C2533" t="n">
-        <v>713.2795496579598</v>
+        <v>713.2795496579596</v>
       </c>
     </row>
     <row r="2534">
@@ -28366,7 +28366,7 @@
         <v>1030</v>
       </c>
       <c r="C2540" t="n">
-        <v>1044.100810209216</v>
+        <v>1044.100810209215</v>
       </c>
     </row>
     <row r="2541">
@@ -28553,7 +28553,7 @@
         <v>766</v>
       </c>
       <c r="C2557" t="n">
-        <v>786.9037626820542</v>
+        <v>786.9037626820541</v>
       </c>
     </row>
     <row r="2558">
@@ -28630,7 +28630,7 @@
         <v>1114</v>
       </c>
       <c r="C2564" t="n">
-        <v>1110.014467331122</v>
+        <v>1110.014467331121</v>
       </c>
     </row>
     <row r="2565">
@@ -28795,7 +28795,7 @@
         <v>190</v>
       </c>
       <c r="C2579" t="n">
-        <v>186.7057949200397</v>
+        <v>186.7057949200398</v>
       </c>
     </row>
     <row r="2580">
@@ -29147,7 +29147,7 @@
         <v>1161</v>
       </c>
       <c r="C2611" t="n">
-        <v>1143.075757061664</v>
+        <v>1143.075757061665</v>
       </c>
     </row>
     <row r="2612">
@@ -29169,7 +29169,7 @@
         <v>1046</v>
       </c>
       <c r="C2613" t="n">
-        <v>1218.845415657167</v>
+        <v>1218.845415657166</v>
       </c>
     </row>
     <row r="2614">
@@ -29224,7 +29224,7 @@
         <v>1094</v>
       </c>
       <c r="C2618" t="n">
-        <v>1112.870291349463</v>
+        <v>1112.870291349464</v>
       </c>
     </row>
     <row r="2619">
@@ -29246,7 +29246,7 @@
         <v>816</v>
       </c>
       <c r="C2620" t="n">
-        <v>863.9386294300398</v>
+        <v>863.9386294300399</v>
       </c>
     </row>
     <row r="2621">
@@ -29268,7 +29268,7 @@
         <v>692</v>
       </c>
       <c r="C2622" t="n">
-        <v>697.4187561913191</v>
+        <v>697.4187561913193</v>
       </c>
     </row>
     <row r="2623">
@@ -29356,7 +29356,7 @@
         <v>704</v>
       </c>
       <c r="C2630" t="n">
-        <v>708.1652008039013</v>
+        <v>708.1652008039014</v>
       </c>
     </row>
     <row r="2631">
@@ -29378,7 +29378,7 @@
         <v>920</v>
       </c>
       <c r="C2632" t="n">
-        <v>773.6474059911829</v>
+        <v>773.6474059911831</v>
       </c>
     </row>
     <row r="2633">
@@ -29400,7 +29400,7 @@
         <v>1614</v>
       </c>
       <c r="C2634" t="n">
-        <v>1418.273776721396</v>
+        <v>1418.273776721395</v>
       </c>
     </row>
     <row r="2635">
@@ -29488,7 +29488,7 @@
         <v>1576</v>
       </c>
       <c r="C2642" t="n">
-        <v>1416.545517715443</v>
+        <v>1416.545517715444</v>
       </c>
     </row>
     <row r="2643">
@@ -29543,7 +29543,7 @@
         <v>211</v>
       </c>
       <c r="C2647" t="n">
-        <v>404.662641964161</v>
+        <v>404.6626419641611</v>
       </c>
     </row>
     <row r="2648">
@@ -29576,7 +29576,7 @@
         <v>144</v>
       </c>
       <c r="C2650" t="n">
-        <v>123.6864576389612</v>
+        <v>123.6864576389613</v>
       </c>
     </row>
     <row r="2651">
@@ -29598,7 +29598,7 @@
         <v>402</v>
       </c>
       <c r="C2652" t="n">
-        <v>369.9559960289709</v>
+        <v>369.955996028971</v>
       </c>
     </row>
     <row r="2653">
@@ -29609,7 +29609,7 @@
         <v>836</v>
       </c>
       <c r="C2653" t="n">
-        <v>813.0505996090517</v>
+        <v>813.0505996090516</v>
       </c>
     </row>
     <row r="2654">
@@ -29675,7 +29675,7 @@
         <v>1026</v>
       </c>
       <c r="C2659" t="n">
-        <v>1063.732551611737</v>
+        <v>1063.732551611738</v>
       </c>
     </row>
     <row r="2660">
@@ -29763,7 +29763,7 @@
         <v>709</v>
       </c>
       <c r="C2667" t="n">
-        <v>778.7811334907252</v>
+        <v>778.7811334907254</v>
       </c>
     </row>
     <row r="2668">
@@ -29807,7 +29807,7 @@
         <v>204</v>
       </c>
       <c r="C2671" t="n">
-        <v>203.2132610428592</v>
+        <v>203.2132610428593</v>
       </c>
     </row>
     <row r="2672">
@@ -29873,7 +29873,7 @@
         <v>740</v>
       </c>
       <c r="C2677" t="n">
-        <v>802.5895543703259</v>
+        <v>802.5895543703258</v>
       </c>
     </row>
     <row r="2678">
@@ -29906,7 +29906,7 @@
         <v>1084</v>
       </c>
       <c r="C2680" t="n">
-        <v>1153.328969848114</v>
+        <v>1153.328969848113</v>
       </c>
     </row>
     <row r="2681">
@@ -30038,7 +30038,7 @@
         <v>602</v>
       </c>
       <c r="C2692" t="n">
-        <v>638.2123712434882</v>
+        <v>638.2123712434883</v>
       </c>
     </row>
     <row r="2693">
@@ -30060,7 +30060,7 @@
         <v>398</v>
       </c>
       <c r="C2694" t="n">
-        <v>411.4409954469021</v>
+        <v>411.440995446902</v>
       </c>
     </row>
     <row r="2695">
@@ -30126,7 +30126,7 @@
         <v>383</v>
       </c>
       <c r="C2700" t="n">
-        <v>390.7962064519163</v>
+        <v>390.7962064519164</v>
       </c>
     </row>
     <row r="2701">
@@ -30137,7 +30137,7 @@
         <v>894</v>
       </c>
       <c r="C2701" t="n">
-        <v>822.8436510747097</v>
+        <v>822.8436510747098</v>
       </c>
     </row>
     <row r="2702">
@@ -30148,7 +30148,7 @@
         <v>1426</v>
       </c>
       <c r="C2702" t="n">
-        <v>1148.932199095262</v>
+        <v>1148.932199095263</v>
       </c>
     </row>
     <row r="2703">
@@ -30335,7 +30335,7 @@
         <v>398</v>
       </c>
       <c r="C2719" t="n">
-        <v>333.7469304486697</v>
+        <v>333.7469304486698</v>
       </c>
     </row>
     <row r="2720">
@@ -30346,7 +30346,7 @@
         <v>301</v>
       </c>
       <c r="C2720" t="n">
-        <v>289.6725562805041</v>
+        <v>289.672556280504</v>
       </c>
     </row>
     <row r="2721">
@@ -30588,7 +30588,7 @@
         <v>722</v>
       </c>
       <c r="C2742" t="n">
-        <v>689.6278438485543</v>
+        <v>689.6278438485544</v>
       </c>
     </row>
     <row r="2743">
@@ -30654,7 +30654,7 @@
         <v>740</v>
       </c>
       <c r="C2748" t="n">
-        <v>709.5816584358593</v>
+        <v>709.5816584358591</v>
       </c>
     </row>
     <row r="2749">
@@ -30687,7 +30687,7 @@
         <v>740</v>
       </c>
       <c r="C2751" t="n">
-        <v>692.2627673577838</v>
+        <v>692.2627673577839</v>
       </c>
     </row>
     <row r="2752">
@@ -30731,7 +30731,7 @@
         <v>1704</v>
       </c>
       <c r="C2755" t="n">
-        <v>1427.982301474335</v>
+        <v>1427.982301474334</v>
       </c>
     </row>
     <row r="2756">
@@ -30753,7 +30753,7 @@
         <v>1784</v>
       </c>
       <c r="C2757" t="n">
-        <v>1699.738811093587</v>
+        <v>1699.738811093586</v>
       </c>
     </row>
     <row r="2758">
@@ -30797,7 +30797,7 @@
         <v>1600</v>
       </c>
       <c r="C2761" t="n">
-        <v>1570.635578106914</v>
+        <v>1570.635578106913</v>
       </c>
     </row>
     <row r="2762">
@@ -31050,7 +31050,7 @@
         <v>1020</v>
       </c>
       <c r="C2784" t="n">
-        <v>1033.771768037691</v>
+        <v>1033.771768037692</v>
       </c>
     </row>
     <row r="2785">
@@ -31072,7 +31072,7 @@
         <v>937</v>
       </c>
       <c r="C2786" t="n">
-        <v>999.7841826101904</v>
+        <v>999.7841826101907</v>
       </c>
     </row>
     <row r="2787">
@@ -31094,7 +31094,7 @@
         <v>547</v>
       </c>
       <c r="C2788" t="n">
-        <v>606.0315147636015</v>
+        <v>606.0315147636016</v>
       </c>
     </row>
     <row r="2789">
@@ -31105,7 +31105,7 @@
         <v>450</v>
       </c>
       <c r="C2789" t="n">
-        <v>465.6916548045454</v>
+        <v>465.6916548045455</v>
       </c>
     </row>
     <row r="2790">
@@ -31116,7 +31116,7 @@
         <v>340</v>
       </c>
       <c r="C2790" t="n">
-        <v>338.680820181334</v>
+        <v>338.6808201813341</v>
       </c>
     </row>
     <row r="2791">
@@ -31325,7 +31325,7 @@
         <v>1107</v>
       </c>
       <c r="C2809" t="n">
-        <v>1073.573957283747</v>
+        <v>1073.573957283746</v>
       </c>
     </row>
     <row r="2810">
@@ -31446,7 +31446,7 @@
         <v>486</v>
       </c>
       <c r="C2820" t="n">
-        <v>391.2605847005097</v>
+        <v>391.2605847005098</v>
       </c>
     </row>
     <row r="2821">
@@ -31589,7 +31589,7 @@
         <v>1098</v>
       </c>
       <c r="C2833" t="n">
-        <v>1069.784911446582</v>
+        <v>1069.784911446583</v>
       </c>
     </row>
     <row r="2834">
@@ -31622,7 +31622,7 @@
         <v>716</v>
       </c>
       <c r="C2836" t="n">
-        <v>777.9598950831822</v>
+        <v>777.959895083182</v>
       </c>
     </row>
     <row r="2837">
@@ -31765,7 +31765,7 @@
         <v>1162</v>
       </c>
       <c r="C2849" t="n">
-        <v>1135.724639871195</v>
+        <v>1135.724639871196</v>
       </c>
     </row>
     <row r="2850">
@@ -31842,7 +31842,7 @@
         <v>1100</v>
       </c>
       <c r="C2856" t="n">
-        <v>1077.244597020453</v>
+        <v>1077.244597020452</v>
       </c>
     </row>
     <row r="2857">
@@ -31886,7 +31886,7 @@
         <v>812</v>
       </c>
       <c r="C2860" t="n">
-        <v>907.3279009421707</v>
+        <v>907.3279009421706</v>
       </c>
     </row>
     <row r="2861">
@@ -31897,7 +31897,7 @@
         <v>691</v>
       </c>
       <c r="C2861" t="n">
-        <v>721.7925550949227</v>
+        <v>721.7925550949228</v>
       </c>
     </row>
     <row r="2862">
@@ -31908,7 +31908,7 @@
         <v>704</v>
       </c>
       <c r="C2862" t="n">
-        <v>712.0403576632156</v>
+        <v>712.0403576632154</v>
       </c>
     </row>
     <row r="2863">
@@ -31974,7 +31974,7 @@
         <v>930</v>
       </c>
       <c r="C2868" t="n">
-        <v>536.1158802389813</v>
+        <v>536.1158802389814</v>
       </c>
     </row>
     <row r="2869">
@@ -31985,7 +31985,7 @@
         <v>1007</v>
       </c>
       <c r="C2869" t="n">
-        <v>661.1456395013686</v>
+        <v>661.1456395013687</v>
       </c>
     </row>
     <row r="2870">
@@ -31996,7 +31996,7 @@
         <v>946</v>
       </c>
       <c r="C2870" t="n">
-        <v>680.9835715742037</v>
+        <v>680.9835715742036</v>
       </c>
     </row>
     <row r="2871">
@@ -32007,7 +32007,7 @@
         <v>761</v>
       </c>
       <c r="C2871" t="n">
-        <v>658.8590860813539</v>
+        <v>658.8590860813538</v>
       </c>
     </row>
     <row r="2872">
@@ -32018,7 +32018,7 @@
         <v>1116</v>
       </c>
       <c r="C2872" t="n">
-        <v>628.3942418389512</v>
+        <v>628.3942418389511</v>
       </c>
     </row>
     <row r="2873">
@@ -32172,7 +32172,7 @@
         <v>907</v>
       </c>
       <c r="C2886" t="n">
-        <v>787.3039654644381</v>
+        <v>787.303965464438</v>
       </c>
     </row>
     <row r="2887">
@@ -32194,7 +32194,7 @@
         <v>168</v>
       </c>
       <c r="C2888" t="n">
-        <v>175.383264863939</v>
+        <v>175.3832648639391</v>
       </c>
     </row>
     <row r="2889">
@@ -32227,7 +32227,7 @@
         <v>190</v>
       </c>
       <c r="C2891" t="n">
-        <v>182.1355077160237</v>
+        <v>182.1355077160236</v>
       </c>
     </row>
     <row r="2892">
@@ -32326,7 +32326,7 @@
         <v>1058</v>
       </c>
       <c r="C2900" t="n">
-        <v>937.1997076342949</v>
+        <v>937.1997076342948</v>
       </c>
     </row>
     <row r="2901">
@@ -32348,7 +32348,7 @@
         <v>1086</v>
       </c>
       <c r="C2902" t="n">
-        <v>910.12692951872</v>
+        <v>910.1269295187199</v>
       </c>
     </row>
     <row r="2903">
@@ -32392,7 +32392,7 @@
         <v>1024</v>
       </c>
       <c r="C2906" t="n">
-        <v>1109.770923626419</v>
+        <v>1109.77092362642</v>
       </c>
     </row>
     <row r="2907">
@@ -32436,7 +32436,7 @@
         <v>382</v>
       </c>
       <c r="C2910" t="n">
-        <v>348.5451088314966</v>
+        <v>348.5451088314965</v>
       </c>
     </row>
     <row r="2911">
@@ -32469,7 +32469,7 @@
         <v>135</v>
       </c>
       <c r="C2913" t="n">
-        <v>138.6804880128668</v>
+        <v>138.6804880128669</v>
       </c>
     </row>
     <row r="2914">
@@ -32491,7 +32491,7 @@
         <v>179</v>
       </c>
       <c r="C2915" t="n">
-        <v>178.4418693486548</v>
+        <v>178.4418693486549</v>
       </c>
     </row>
     <row r="2916">
@@ -32513,7 +32513,7 @@
         <v>786</v>
       </c>
       <c r="C2917" t="n">
-        <v>746.3821270623135</v>
+        <v>746.3821270623137</v>
       </c>
     </row>
     <row r="2918">
@@ -32612,7 +32612,7 @@
         <v>1107</v>
       </c>
       <c r="C2926" t="n">
-        <v>1105.64200628739</v>
+        <v>1105.642006287389</v>
       </c>
     </row>
     <row r="2927">
@@ -32634,7 +32634,7 @@
         <v>1172</v>
       </c>
       <c r="C2928" t="n">
-        <v>1140.547149268337</v>
+        <v>1140.547149268336</v>
       </c>
     </row>
     <row r="2929">
@@ -32667,7 +32667,7 @@
         <v>900</v>
       </c>
       <c r="C2931" t="n">
-        <v>946.2516509520381</v>
+        <v>946.2516509520383</v>
       </c>
     </row>
     <row r="2932">
@@ -32821,7 +32821,7 @@
         <v>776</v>
       </c>
       <c r="C2945" t="n">
-        <v>988.8268205925527</v>
+        <v>988.8268205925528</v>
       </c>
     </row>
     <row r="2946">
@@ -32832,7 +32832,7 @@
         <v>705</v>
       </c>
       <c r="C2946" t="n">
-        <v>942.0766332129659</v>
+        <v>942.0766332129662</v>
       </c>
     </row>
     <row r="2947">
@@ -32843,7 +32843,7 @@
         <v>436</v>
       </c>
       <c r="C2947" t="n">
-        <v>988.34963011312</v>
+        <v>988.3496301131203</v>
       </c>
     </row>
     <row r="2948">
@@ -32876,7 +32876,7 @@
         <v>1118</v>
       </c>
       <c r="C2950" t="n">
-        <v>1153.056562686719</v>
+        <v>1153.05656268672</v>
       </c>
     </row>
     <row r="2951">
@@ -33041,7 +33041,7 @@
         <v>938</v>
       </c>
       <c r="C2965" t="n">
-        <v>780.0565430539926</v>
+        <v>780.0565430539925</v>
       </c>
     </row>
     <row r="2966">
@@ -33096,7 +33096,7 @@
         <v>1184</v>
       </c>
       <c r="C2970" t="n">
-        <v>1146.697898839904</v>
+        <v>1146.697898839905</v>
       </c>
     </row>
     <row r="2971">
@@ -33107,7 +33107,7 @@
         <v>1185</v>
       </c>
       <c r="C2971" t="n">
-        <v>1156.064976782802</v>
+        <v>1156.064976782803</v>
       </c>
     </row>
     <row r="2972">
@@ -33162,7 +33162,7 @@
         <v>1094</v>
       </c>
       <c r="C2976" t="n">
-        <v>1105.637449099643</v>
+        <v>1105.637449099642</v>
       </c>
     </row>
     <row r="2977">
@@ -33217,7 +33217,7 @@
         <v>800</v>
       </c>
       <c r="C2981" t="n">
-        <v>799.3723823033137</v>
+        <v>799.3723823033138</v>
       </c>
     </row>
     <row r="2982">
@@ -33228,7 +33228,7 @@
         <v>744</v>
       </c>
       <c r="C2982" t="n">
-        <v>691.3154547815654</v>
+        <v>691.3154547815657</v>
       </c>
     </row>
     <row r="2983">
@@ -33239,7 +33239,7 @@
         <v>1535</v>
       </c>
       <c r="C2983" t="n">
-        <v>1361.372810024679</v>
+        <v>1361.372810024678</v>
       </c>
     </row>
     <row r="2984">
@@ -33305,7 +33305,7 @@
         <v>802</v>
       </c>
       <c r="C2989" t="n">
-        <v>711.8200005882064</v>
+        <v>711.8200005882063</v>
       </c>
     </row>
     <row r="2990">
@@ -33316,7 +33316,7 @@
         <v>762</v>
       </c>
       <c r="C2990" t="n">
-        <v>731.131186815571</v>
+        <v>731.1311868155711</v>
       </c>
     </row>
     <row r="2991">
@@ -33327,7 +33327,7 @@
         <v>780</v>
       </c>
       <c r="C2991" t="n">
-        <v>707.8893495640019</v>
+        <v>707.889349564002</v>
       </c>
     </row>
     <row r="2992">
@@ -33371,7 +33371,7 @@
         <v>1810</v>
       </c>
       <c r="C2995" t="n">
-        <v>1647.669376482685</v>
+        <v>1647.669376482686</v>
       </c>
     </row>
     <row r="2996">
@@ -33382,7 +33382,7 @@
         <v>772</v>
       </c>
       <c r="C2996" t="n">
-        <v>1674.160854394466</v>
+        <v>1674.160854394467</v>
       </c>
     </row>
     <row r="2997">
@@ -33470,7 +33470,7 @@
         <v>1224</v>
       </c>
       <c r="C3004" t="n">
-        <v>1280.487400133708</v>
+        <v>1280.487400133707</v>
       </c>
     </row>
     <row r="3005">
@@ -33558,7 +33558,7 @@
         <v>386</v>
       </c>
       <c r="C3012" t="n">
-        <v>397.5111087257308</v>
+        <v>397.5111087257309</v>
       </c>
     </row>
     <row r="3013">
@@ -33646,7 +33646,7 @@
         <v>1085</v>
       </c>
       <c r="C3020" t="n">
-        <v>1312.87157151186</v>
+        <v>1312.871571511859</v>
       </c>
     </row>
     <row r="3021">
@@ -33800,7 +33800,7 @@
         <v>128</v>
       </c>
       <c r="C3034" t="n">
-        <v>139.0761241464213</v>
+        <v>139.0761241464214</v>
       </c>
     </row>
     <row r="3035">
@@ -33844,7 +33844,7 @@
         <v>1470</v>
       </c>
       <c r="C3038" t="n">
-        <v>1177.667751758724</v>
+        <v>1177.667751758723</v>
       </c>
     </row>
     <row r="3039">
@@ -33943,7 +33943,7 @@
         <v>1150</v>
       </c>
       <c r="C3047" t="n">
-        <v>1127.217237326607</v>
+        <v>1127.217237326606</v>
       </c>
     </row>
     <row r="3048">
@@ -34053,7 +34053,7 @@
         <v>188</v>
       </c>
       <c r="C3057" t="n">
-        <v>198.2831702134828</v>
+        <v>198.2831702134827</v>
       </c>
     </row>
     <row r="3058">
@@ -34086,7 +34086,7 @@
         <v>390</v>
       </c>
       <c r="C3060" t="n">
-        <v>425.2598786777306</v>
+        <v>425.2598786777307</v>
       </c>
     </row>
     <row r="3061">
@@ -34097,7 +34097,7 @@
         <v>836</v>
       </c>
       <c r="C3061" t="n">
-        <v>820.8335021916843</v>
+        <v>820.8335021916841</v>
       </c>
     </row>
     <row r="3062">
@@ -34130,7 +34130,7 @@
         <v>1202</v>
       </c>
       <c r="C3064" t="n">
-        <v>1259.15652748292</v>
+        <v>1259.156527482921</v>
       </c>
     </row>
     <row r="3065">
@@ -34152,7 +34152,7 @@
         <v>1158</v>
       </c>
       <c r="C3066" t="n">
-        <v>1173.841781166995</v>
+        <v>1173.841781166996</v>
       </c>
     </row>
     <row r="3067">
@@ -34174,7 +34174,7 @@
         <v>1206</v>
       </c>
       <c r="C3068" t="n">
-        <v>1147.232612900235</v>
+        <v>1147.232612900236</v>
       </c>
     </row>
     <row r="3069">
@@ -34185,7 +34185,7 @@
         <v>1141</v>
       </c>
       <c r="C3069" t="n">
-        <v>1184.175593679604</v>
+        <v>1184.175593679603</v>
       </c>
     </row>
     <row r="3070">
@@ -34306,7 +34306,7 @@
         <v>339</v>
       </c>
       <c r="C3080" t="n">
-        <v>323.9300783710174</v>
+        <v>323.9300783710175</v>
       </c>
     </row>
     <row r="3081">
@@ -34339,7 +34339,7 @@
         <v>240</v>
       </c>
       <c r="C3083" t="n">
-        <v>238.8578538928229</v>
+        <v>238.8578538928228</v>
       </c>
     </row>
     <row r="3084">
@@ -34493,7 +34493,7 @@
         <v>1194</v>
       </c>
       <c r="C3097" t="n">
-        <v>1122.381416880735</v>
+        <v>1122.381416880736</v>
       </c>
     </row>
     <row r="3098">
@@ -34537,7 +34537,7 @@
         <v>831</v>
       </c>
       <c r="C3101" t="n">
-        <v>805.5425245645129</v>
+        <v>805.542524564513</v>
       </c>
     </row>
     <row r="3102">
@@ -34603,7 +34603,7 @@
         <v>818</v>
       </c>
       <c r="C3107" t="n">
-        <v>752.154930809374</v>
+        <v>752.1549308093742</v>
       </c>
     </row>
     <row r="3108">
@@ -34614,7 +34614,7 @@
         <v>851</v>
       </c>
       <c r="C3108" t="n">
-        <v>719.8493767939872</v>
+        <v>719.8493767939873</v>
       </c>
     </row>
     <row r="3109">
@@ -34735,7 +34735,7 @@
         <v>1449</v>
       </c>
       <c r="C3119" t="n">
-        <v>1507.804985126255</v>
+        <v>1507.804985126256</v>
       </c>
     </row>
     <row r="3120">
@@ -34768,7 +34768,7 @@
         <v>1525</v>
       </c>
       <c r="C3122" t="n">
-        <v>1496.26774599863</v>
+        <v>1496.267745998629</v>
       </c>
     </row>
     <row r="3123">
@@ -34900,7 +34900,7 @@
         <v>1099</v>
       </c>
       <c r="C3134" t="n">
-        <v>1417.209079229411</v>
+        <v>1417.20907922941</v>
       </c>
     </row>
     <row r="3135">
@@ -35098,7 +35098,7 @@
         <v>166</v>
       </c>
       <c r="C3152" t="n">
-        <v>175.7756765635056</v>
+        <v>175.7756765635057</v>
       </c>
     </row>
     <row r="3153">
@@ -35142,7 +35142,7 @@
         <v>512</v>
       </c>
       <c r="C3156" t="n">
-        <v>385.3873765792142</v>
+        <v>385.3873765792143</v>
       </c>
     </row>
     <row r="3157">
@@ -35230,7 +35230,7 @@
         <v>1156</v>
       </c>
       <c r="C3164" t="n">
-        <v>1093.520003850458</v>
+        <v>1093.520003850457</v>
       </c>
     </row>
     <row r="3165">
@@ -35274,7 +35274,7 @@
         <v>1152</v>
       </c>
       <c r="C3168" t="n">
-        <v>1136.278559862756</v>
+        <v>1136.278559862757</v>
       </c>
     </row>
     <row r="3169">
@@ -35340,7 +35340,7 @@
         <v>451</v>
       </c>
       <c r="C3174" t="n">
-        <v>440.8667707692741</v>
+        <v>440.866770769274</v>
       </c>
     </row>
     <row r="3175">
@@ -35417,7 +35417,7 @@
         <v>905</v>
       </c>
       <c r="C3181" t="n">
-        <v>833.1700238508912</v>
+        <v>833.1700238508913</v>
       </c>
     </row>
     <row r="3182">
@@ -35582,7 +35582,7 @@
         <v>846</v>
       </c>
       <c r="C3196" t="n">
-        <v>873.548715731444</v>
+        <v>873.5487157314441</v>
       </c>
     </row>
     <row r="3197">
@@ -35604,7 +35604,7 @@
         <v>580</v>
       </c>
       <c r="C3198" t="n">
-        <v>604.1494829577862</v>
+        <v>604.1494829577861</v>
       </c>
     </row>
     <row r="3199">
@@ -35648,7 +35648,7 @@
         <v>220</v>
       </c>
       <c r="C3202" t="n">
-        <v>222.6617149385804</v>
+        <v>222.6617149385803</v>
       </c>
     </row>
     <row r="3203">
@@ -35714,7 +35714,7 @@
         <v>1152</v>
       </c>
       <c r="C3208" t="n">
-        <v>1116.232716194452</v>
+        <v>1116.232716194451</v>
       </c>
     </row>
     <row r="3209">
@@ -35868,7 +35868,7 @@
         <v>730</v>
       </c>
       <c r="C3222" t="n">
-        <v>699.4005570239013</v>
+        <v>699.4005570239012</v>
       </c>
     </row>
     <row r="3223">
@@ -35934,7 +35934,7 @@
         <v>782</v>
       </c>
       <c r="C3228" t="n">
-        <v>713.5928891588826</v>
+        <v>713.5928891588825</v>
       </c>
     </row>
     <row r="3229">
@@ -35945,7 +35945,7 @@
         <v>768</v>
       </c>
       <c r="C3229" t="n">
-        <v>711.489601540601</v>
+        <v>711.4896015406008</v>
       </c>
     </row>
     <row r="3230">
@@ -35956,7 +35956,7 @@
         <v>644</v>
       </c>
       <c r="C3230" t="n">
-        <v>714.9248006852438</v>
+        <v>714.924800685244</v>
       </c>
     </row>
     <row r="3231">
@@ -35978,7 +35978,7 @@
         <v>1027</v>
       </c>
       <c r="C3232" t="n">
-        <v>834.9118053850834</v>
+        <v>834.9118053850833</v>
       </c>
     </row>
     <row r="3233">
@@ -36088,7 +36088,7 @@
         <v>1578</v>
       </c>
       <c r="C3242" t="n">
-        <v>1573.97195101831</v>
+        <v>1573.971951018309</v>
       </c>
     </row>
     <row r="3243">
@@ -36176,7 +36176,7 @@
         <v>139</v>
       </c>
       <c r="C3250" t="n">
-        <v>140.3642062035828</v>
+        <v>140.3642062035827</v>
       </c>
     </row>
     <row r="3251">
@@ -36253,7 +36253,7 @@
         <v>1138</v>
       </c>
       <c r="C3257" t="n">
-        <v>1168.62854648931</v>
+        <v>1168.628546489311</v>
       </c>
     </row>
     <row r="3258">
@@ -36352,7 +36352,7 @@
         <v>1012</v>
       </c>
       <c r="C3266" t="n">
-        <v>1064.176125790501</v>
+        <v>1064.176125790502</v>
       </c>
     </row>
     <row r="3267">
@@ -36473,7 +36473,7 @@
         <v>848</v>
       </c>
       <c r="C3277" t="n">
-        <v>739.0800492303894</v>
+        <v>739.0800492303896</v>
       </c>
     </row>
     <row r="3278">
@@ -36726,7 +36726,7 @@
         <v>410</v>
       </c>
       <c r="C3300" t="n">
-        <v>415.380907600661</v>
+        <v>415.3809076006609</v>
       </c>
     </row>
     <row r="3301">
@@ -36737,7 +36737,7 @@
         <v>904</v>
       </c>
       <c r="C3301" t="n">
-        <v>753.9303276899992</v>
+        <v>753.9303276899994</v>
       </c>
     </row>
     <row r="3302">
@@ -36792,7 +36792,7 @@
         <v>1173</v>
       </c>
       <c r="C3306" t="n">
-        <v>1180.93618855717</v>
+        <v>1180.936188557171</v>
       </c>
     </row>
     <row r="3307">
@@ -36814,7 +36814,7 @@
         <v>1188</v>
       </c>
       <c r="C3308" t="n">
-        <v>1141.372951566805</v>
+        <v>1141.372951566806</v>
       </c>
     </row>
     <row r="3309">
@@ -37001,7 +37001,7 @@
         <v>911</v>
       </c>
       <c r="C3325" t="n">
-        <v>773.5181468765094</v>
+        <v>773.5181468765093</v>
       </c>
     </row>
     <row r="3326">
@@ -37012,7 +37012,7 @@
         <v>979</v>
       </c>
       <c r="C3326" t="n">
-        <v>1350.467562093614</v>
+        <v>1350.467562093613</v>
       </c>
     </row>
     <row r="3327">
@@ -37232,7 +37232,7 @@
         <v>862</v>
       </c>
       <c r="C3346" t="n">
-        <v>861.2295508927861</v>
+        <v>861.2295508927858</v>
       </c>
     </row>
     <row r="3347">
@@ -37254,7 +37254,7 @@
         <v>799</v>
       </c>
       <c r="C3348" t="n">
-        <v>711.5088016425802</v>
+        <v>711.5088016425801</v>
       </c>
     </row>
     <row r="3349">
@@ -37276,7 +37276,7 @@
         <v>670</v>
       </c>
       <c r="C3350" t="n">
-        <v>710.8729653176244</v>
+        <v>710.8729653176247</v>
       </c>
     </row>
     <row r="3351">
@@ -37375,7 +37375,7 @@
         <v>1620</v>
       </c>
       <c r="C3359" t="n">
-        <v>1478.839351473011</v>
+        <v>1478.83935147301</v>
       </c>
     </row>
     <row r="3360">
@@ -37386,7 +37386,7 @@
         <v>1553</v>
       </c>
       <c r="C3360" t="n">
-        <v>1552.024752082388</v>
+        <v>1552.024752082389</v>
       </c>
     </row>
     <row r="3361">
@@ -37452,7 +37452,7 @@
         <v>1154</v>
       </c>
       <c r="C3366" t="n">
-        <v>950.7948975829646</v>
+        <v>950.7948975829645</v>
       </c>
     </row>
     <row r="3367">
@@ -37463,7 +37463,7 @@
         <v>242</v>
       </c>
       <c r="C3367" t="n">
-        <v>444.1341807786831</v>
+        <v>444.1341807786832</v>
       </c>
     </row>
     <row r="3368">
@@ -37474,7 +37474,7 @@
         <v>198</v>
       </c>
       <c r="C3368" t="n">
-        <v>175.2104050496717</v>
+        <v>175.2104050496718</v>
       </c>
     </row>
     <row r="3369">
@@ -37595,7 +37595,7 @@
         <v>836</v>
       </c>
       <c r="C3379" t="n">
-        <v>976.4724987023795</v>
+        <v>976.4724987023797</v>
       </c>
     </row>
     <row r="3380">
@@ -37606,7 +37606,7 @@
         <v>366</v>
       </c>
       <c r="C3380" t="n">
-        <v>903.0500635359881</v>
+        <v>903.050063535988</v>
       </c>
     </row>
     <row r="3381">
@@ -37617,7 +37617,7 @@
         <v>976</v>
       </c>
       <c r="C3381" t="n">
-        <v>841.2128431379623</v>
+        <v>841.2128431379622</v>
       </c>
     </row>
     <row r="3382">
@@ -37683,7 +37683,7 @@
         <v>776</v>
       </c>
       <c r="C3387" t="n">
-        <v>825.1278027304261</v>
+        <v>825.1278027304263</v>
       </c>
     </row>
     <row r="3388">
@@ -37716,7 +37716,7 @@
         <v>344</v>
       </c>
       <c r="C3390" t="n">
-        <v>334.2897142512972</v>
+        <v>334.2897142512971</v>
       </c>
     </row>
     <row r="3391">
@@ -37782,7 +37782,7 @@
         <v>386</v>
       </c>
       <c r="C3396" t="n">
-        <v>394.6600513000381</v>
+        <v>394.6600513000382</v>
       </c>
     </row>
     <row r="3397">
@@ -37804,7 +37804,7 @@
         <v>1054</v>
       </c>
       <c r="C3398" t="n">
-        <v>1260.985859378576</v>
+        <v>1260.985859378577</v>
       </c>
     </row>
     <row r="3399">
@@ -37947,7 +37947,7 @@
         <v>792</v>
       </c>
       <c r="C3411" t="n">
-        <v>908.9150710098359</v>
+        <v>908.915071009836</v>
       </c>
     </row>
     <row r="3412">
@@ -37991,7 +37991,7 @@
         <v>278</v>
       </c>
       <c r="C3415" t="n">
-        <v>297.5365168253185</v>
+        <v>297.5365168253184</v>
       </c>
     </row>
     <row r="3416">
@@ -38002,7 +38002,7 @@
         <v>207</v>
       </c>
       <c r="C3416" t="n">
-        <v>191.9263717231138</v>
+        <v>191.9263717231137</v>
       </c>
     </row>
     <row r="3417">
@@ -38233,7 +38233,7 @@
         <v>649</v>
       </c>
       <c r="C3437" t="n">
-        <v>674.9953685322632</v>
+        <v>674.9953685322631</v>
       </c>
     </row>
     <row r="3438">
@@ -38266,7 +38266,7 @@
         <v>296</v>
       </c>
       <c r="C3440" t="n">
-        <v>301.2810050159439</v>
+        <v>301.2810050159438</v>
       </c>
     </row>
     <row r="3441">
@@ -38277,7 +38277,7 @@
         <v>252</v>
       </c>
       <c r="C3441" t="n">
-        <v>249.3861777793227</v>
+        <v>249.3861777793228</v>
       </c>
     </row>
     <row r="3442">
@@ -38497,7 +38497,7 @@
         <v>708</v>
       </c>
       <c r="C3461" t="n">
-        <v>721.9066914360078</v>
+        <v>721.9066914360079</v>
       </c>
     </row>
     <row r="3462">
@@ -38552,7 +38552,7 @@
         <v>922</v>
       </c>
       <c r="C3466" t="n">
-        <v>752.1136189464169</v>
+        <v>752.1136189464166</v>
       </c>
     </row>
     <row r="3467">
@@ -38574,7 +38574,7 @@
         <v>792</v>
       </c>
       <c r="C3468" t="n">
-        <v>716.1223748102666</v>
+        <v>716.1223748102668</v>
       </c>
     </row>
     <row r="3469">
@@ -38585,7 +38585,7 @@
         <v>772</v>
       </c>
       <c r="C3469" t="n">
-        <v>733.0921342302886</v>
+        <v>733.0921342302888</v>
       </c>
     </row>
     <row r="3470">
@@ -38596,7 +38596,7 @@
         <v>723</v>
       </c>
       <c r="C3470" t="n">
-        <v>713.9632016564874</v>
+        <v>713.9632016564875</v>
       </c>
     </row>
     <row r="3471">
@@ -38607,7 +38607,7 @@
         <v>778</v>
       </c>
       <c r="C3471" t="n">
-        <v>714.6920107023142</v>
+        <v>714.6920107023143</v>
       </c>
     </row>
     <row r="3472">
@@ -38728,7 +38728,7 @@
         <v>1550</v>
       </c>
       <c r="C3482" t="n">
-        <v>1465.813599491654</v>
+        <v>1465.813599491655</v>
       </c>
     </row>
     <row r="3483">
@@ -38772,7 +38772,7 @@
         <v>837</v>
       </c>
       <c r="C3486" t="n">
-        <v>691.2586317901213</v>
+        <v>691.2586317901212</v>
       </c>
     </row>
     <row r="3487">
@@ -38827,7 +38827,7 @@
         <v>186</v>
       </c>
       <c r="C3491" t="n">
-        <v>176.3851170399768</v>
+        <v>176.3851170399767</v>
       </c>
     </row>
     <row r="3492">
@@ -38849,7 +38849,7 @@
         <v>912</v>
       </c>
       <c r="C3493" t="n">
-        <v>807.2643674382082</v>
+        <v>807.2643674382083</v>
       </c>
     </row>
     <row r="3494">
@@ -39003,7 +39003,7 @@
         <v>766</v>
       </c>
       <c r="C3507" t="n">
-        <v>778.9518129700348</v>
+        <v>778.9518129700351</v>
       </c>
     </row>
     <row r="3508">
@@ -39080,7 +39080,7 @@
         <v>120</v>
       </c>
       <c r="C3514" t="n">
-        <v>128.5846482769417</v>
+        <v>128.5846482769416</v>
       </c>
     </row>
     <row r="3515">
@@ -39190,7 +39190,7 @@
         <v>1104</v>
       </c>
       <c r="C3524" t="n">
-        <v>1096.188341154064</v>
+        <v>1096.188341154063</v>
       </c>
     </row>
     <row r="3525">
@@ -39234,7 +39234,7 @@
         <v>1078</v>
       </c>
       <c r="C3528" t="n">
-        <v>1050.834637432639</v>
+        <v>1050.834637432638</v>
       </c>
     </row>
     <row r="3529">
@@ -39267,7 +39267,7 @@
         <v>820</v>
       </c>
       <c r="C3531" t="n">
-        <v>871.1170354856532</v>
+        <v>871.117035485653</v>
       </c>
     </row>
     <row r="3532">
@@ -39300,7 +39300,7 @@
         <v>398</v>
       </c>
       <c r="C3534" t="n">
-        <v>368.3588477885814</v>
+        <v>368.3588477885815</v>
       </c>
     </row>
     <row r="3535">
@@ -39333,7 +39333,7 @@
         <v>162</v>
       </c>
       <c r="C3537" t="n">
-        <v>148.5915738175171</v>
+        <v>148.591573817517</v>
       </c>
     </row>
     <row r="3538">
@@ -39377,7 +39377,7 @@
         <v>918</v>
       </c>
       <c r="C3541" t="n">
-        <v>784.6706224654424</v>
+        <v>784.6706224654423</v>
       </c>
     </row>
     <row r="3542">
@@ -39421,7 +39421,7 @@
         <v>1151</v>
       </c>
       <c r="C3545" t="n">
-        <v>1168.175932517789</v>
+        <v>1168.17593251779</v>
       </c>
     </row>
     <row r="3546">
@@ -39553,7 +39553,7 @@
         <v>660</v>
       </c>
       <c r="C3557" t="n">
-        <v>687.6160548101599</v>
+        <v>687.61605481016</v>
       </c>
     </row>
     <row r="3558">
@@ -39696,7 +39696,7 @@
         <v>1088</v>
       </c>
       <c r="C3570" t="n">
-        <v>1058.013552537234</v>
+        <v>1058.013552537233</v>
       </c>
     </row>
     <row r="3571">
@@ -39707,7 +39707,7 @@
         <v>1070</v>
       </c>
       <c r="C3571" t="n">
-        <v>1080.987888754281</v>
+        <v>1080.98788875428</v>
       </c>
     </row>
     <row r="3572">
@@ -39762,7 +39762,7 @@
         <v>996</v>
       </c>
       <c r="C3576" t="n">
-        <v>1030.003376769391</v>
+        <v>1030.00337676939</v>
       </c>
     </row>
     <row r="3577">
@@ -39828,7 +39828,7 @@
         <v>750</v>
       </c>
       <c r="C3582" t="n">
-        <v>677.1238048700745</v>
+        <v>677.1238048700747</v>
       </c>
     </row>
     <row r="3583">
@@ -39883,7 +39883,7 @@
         <v>816</v>
       </c>
       <c r="C3587" t="n">
-        <v>701.643482362511</v>
+        <v>701.6434823625111</v>
       </c>
     </row>
     <row r="3588">
@@ -39905,7 +39905,7 @@
         <v>765</v>
       </c>
       <c r="C3589" t="n">
-        <v>692.3248687345184</v>
+        <v>692.3248687345182</v>
       </c>
     </row>
     <row r="3590">
@@ -39916,7 +39916,7 @@
         <v>688</v>
       </c>
       <c r="C3590" t="n">
-        <v>710.7202382605994</v>
+        <v>710.7202382605997</v>
       </c>
     </row>
     <row r="3591">
@@ -39971,7 +39971,7 @@
         <v>1643</v>
       </c>
       <c r="C3595" t="n">
-        <v>1611.605843527169</v>
+        <v>1611.605843527168</v>
       </c>
     </row>
     <row r="3596">
@@ -39982,7 +39982,7 @@
         <v>1684</v>
       </c>
       <c r="C3596" t="n">
-        <v>1677.705935545366</v>
+        <v>1677.705935545367</v>
       </c>
     </row>
     <row r="3597">
@@ -40070,7 +40070,7 @@
         <v>1206</v>
       </c>
       <c r="C3604" t="n">
-        <v>1254.106132144934</v>
+        <v>1254.106132144933</v>
       </c>
     </row>
     <row r="3605">
@@ -40191,7 +40191,7 @@
         <v>1089</v>
       </c>
       <c r="C3615" t="n">
-        <v>1130.745089341955</v>
+        <v>1130.745089341954</v>
       </c>
     </row>
     <row r="3616">
@@ -40664,7 +40664,7 @@
         <v>141</v>
       </c>
       <c r="C3658" t="n">
-        <v>152.6582445910704</v>
+        <v>152.6582445910703</v>
       </c>
     </row>
     <row r="3659">
@@ -40730,7 +40730,7 @@
         <v>1160</v>
       </c>
       <c r="C3664" t="n">
-        <v>1168.168328497533</v>
+        <v>1168.168328497534</v>
       </c>
     </row>
     <row r="3665">
@@ -40851,7 +40851,7 @@
         <v>968</v>
       </c>
       <c r="C3675" t="n">
-        <v>1065.271390844469</v>
+        <v>1065.27139084447</v>
       </c>
     </row>
     <row r="3676">
@@ -40862,7 +40862,7 @@
         <v>756</v>
       </c>
       <c r="C3676" t="n">
-        <v>777.6784514208026</v>
+        <v>777.6784514208025</v>
       </c>
     </row>
     <row r="3677">
@@ -40917,7 +40917,7 @@
         <v>241</v>
       </c>
       <c r="C3681" t="n">
-        <v>247.8252844792606</v>
+        <v>247.8252844792605</v>
       </c>
     </row>
     <row r="3682">
@@ -40961,7 +40961,7 @@
         <v>894</v>
       </c>
       <c r="C3685" t="n">
-        <v>740.6361017891521</v>
+        <v>740.636101789152</v>
       </c>
     </row>
     <row r="3686">
@@ -41071,7 +41071,7 @@
         <v>991</v>
       </c>
       <c r="C3695" t="n">
-        <v>955.1050484227183</v>
+        <v>955.1050484227184</v>
       </c>
     </row>
     <row r="3696">
@@ -41093,7 +41093,7 @@
         <v>988</v>
       </c>
       <c r="C3697" t="n">
-        <v>996.6438952205134</v>
+        <v>996.6438952205135</v>
       </c>
     </row>
     <row r="3698">
@@ -41126,7 +41126,7 @@
         <v>798</v>
       </c>
       <c r="C3700" t="n">
-        <v>868.7403543726646</v>
+        <v>868.7403543726647</v>
       </c>
     </row>
     <row r="3701">
@@ -41148,7 +41148,7 @@
         <v>734</v>
       </c>
       <c r="C3702" t="n">
-        <v>671.2708557097742</v>
+        <v>671.2708557097741</v>
       </c>
     </row>
     <row r="3703">
@@ -41225,7 +41225,7 @@
         <v>800</v>
       </c>
       <c r="C3709" t="n">
-        <v>697.1221368168314</v>
+        <v>697.1221368168312</v>
       </c>
     </row>
     <row r="3710">
@@ -41236,7 +41236,7 @@
         <v>801</v>
       </c>
       <c r="C3710" t="n">
-        <v>730.1321134038616</v>
+        <v>730.1321134038615</v>
       </c>
     </row>
     <row r="3711">
@@ -41258,7 +41258,7 @@
         <v>1104</v>
       </c>
       <c r="C3712" t="n">
-        <v>857.8057535710718</v>
+        <v>857.8057535710719</v>
       </c>
     </row>
     <row r="3713">
@@ -41379,7 +41379,7 @@
         <v>1500</v>
       </c>
       <c r="C3723" t="n">
-        <v>1491.741249320891</v>
+        <v>1491.74124932089</v>
       </c>
     </row>
     <row r="3724">
@@ -41412,7 +41412,7 @@
         <v>1063</v>
       </c>
       <c r="C3726" t="n">
-        <v>792.4732873859446</v>
+        <v>792.4732873859447</v>
       </c>
     </row>
     <row r="3727">
@@ -41643,7 +41643,7 @@
         <v>758</v>
       </c>
       <c r="C3747" t="n">
-        <v>777.6434467261945</v>
+        <v>777.6434467261947</v>
       </c>
     </row>
     <row r="3748">
@@ -41698,7 +41698,7 @@
         <v>124</v>
       </c>
       <c r="C3752" t="n">
-        <v>140.4178913341955</v>
+        <v>140.4178913341954</v>
       </c>
     </row>
     <row r="3753">
@@ -41753,7 +41753,7 @@
         <v>842</v>
       </c>
       <c r="C3757" t="n">
-        <v>779.3832396663939</v>
+        <v>779.3832396663938</v>
       </c>
     </row>
     <row r="3758">
@@ -42006,7 +42006,7 @@
         <v>417</v>
       </c>
       <c r="C3780" t="n">
-        <v>426.3355189395777</v>
+        <v>426.3355189395778</v>
       </c>
     </row>
     <row r="3781">
@@ -42193,7 +42193,7 @@
         <v>670</v>
       </c>
       <c r="C3797" t="n">
-        <v>686.9961832783669</v>
+        <v>686.996183278367</v>
       </c>
     </row>
     <row r="3798">
@@ -42336,7 +42336,7 @@
         <v>1092</v>
       </c>
       <c r="C3810" t="n">
-        <v>1058.576400274484</v>
+        <v>1058.576400274483</v>
       </c>
     </row>
     <row r="3811">
@@ -42424,7 +42424,7 @@
         <v>1066</v>
       </c>
       <c r="C3818" t="n">
-        <v>1010.255733032886</v>
+        <v>1010.255733032885</v>
       </c>
     </row>
     <row r="3819">
@@ -42567,7 +42567,7 @@
         <v>874</v>
       </c>
       <c r="C3831" t="n">
-        <v>807.663271544109</v>
+        <v>807.6632715441089</v>
       </c>
     </row>
     <row r="3832">
